--- a/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/ar-sa.xlsx
+++ b/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/ar-sa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Documents\_Learn\Packaging.tutorial\OS.11\23H2\Expand\Install\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF410B7-72B8-4968-AFB6-9C5603942A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0931E0C2-5643-4859-B05E-EDA8AB777B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="5" r:id="rId1"/>
@@ -826,13 +826,6 @@
     <t>Regional associations file</t>
   </si>
   <si>
-    <t>Microsoft-Windows-LanguageFeatures-Basic-en-us-Package~31bf3856ad364e35~amd64~~10.0.22621.2428
-Microsoft-Windows-LanguageFeatures-OCR-en-us-Package~31bf3856ad364e35~amd64~~10.0.22621.2428</t>
-  </si>
-  <si>
-    <t>en-US</t>
-  </si>
-  <si>
     <t>Report: Windows 11 23H2</t>
   </si>
   <si>
@@ -879,6 +872,19 @@
   <si>
     <t xml:space="preserve">
  7. Windows 11 Enterprise
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+en-US
+ar-EG
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Microsoft-Windows-LanguageFeatures-Basic-en-us-Package~31bf3856ad364e35~amd64~~10.0.22621.2428
+Microsoft-Windows-LanguageFeatures-OCR-en-us-Package~31bf3856ad364e35~amd64~~10.0.22621.2428
+Microsoft-Windows-LanguageFeatures-TextToSpeech-ar-eg-Package~31bf3856ad364e35~amd64~~10.0.22621.2428
 </t>
   </si>
 </sst>
@@ -4735,22 +4741,22 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="84.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="50.3828125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.53515625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="120.69140625" style="3" customWidth="1"/>
-    <col min="8" max="10" width="16.69140625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="16.69140625" style="7" customWidth="1"/>
-    <col min="12" max="12" width="2.69140625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.15234375" style="1" hidden="1"/>
+    <col min="1" max="1" width="2.6640625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="84.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50.3984375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.53125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="120.6640625" style="3" customWidth="1"/>
+    <col min="8" max="10" width="16.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="2.6640625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.1328125" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4763,10 +4769,10 @@
       <c r="J1" s="2"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" ht="80.2" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="1"/>
       <c r="C2" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -4779,7 +4785,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
       <c r="C3" s="6"/>
       <c r="D3" s="5"/>
@@ -4791,7 +4797,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="5.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" ht="5.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -4802,7 +4808,7 @@
       <c r="I4" s="10"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:12" ht="62.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" ht="62.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
         <v>9</v>
@@ -4833,22 +4839,22 @@
       </c>
       <c r="L5" s="7"/>
     </row>
-    <row r="6" spans="1:12" ht="126.9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" ht="126" x14ac:dyDescent="0.45">
       <c r="B6" s="13"/>
       <c r="C6" s="14" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>251</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="H6" s="13">
         <v>1</v>
@@ -4862,22 +4868,22 @@
       <c r="K6" s="13"/>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="1:12" ht="47.6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" ht="94.5" x14ac:dyDescent="0.45">
       <c r="B7" s="13"/>
       <c r="C7" s="45" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D7" s="45" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E7" s="46" t="s">
         <v>251</v>
       </c>
       <c r="F7" s="47" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="H7" s="13">
         <v>1</v>
@@ -4891,7 +4897,7 @@
       <c r="K7" s="46"/>
       <c r="L7" s="7"/>
     </row>
-    <row r="8" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" ht="20.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C8" s="13"/>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
@@ -4901,7 +4907,7 @@
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>
     </row>
-    <row r="9" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B9" s="16"/>
       <c r="C9" s="17" t="s">
         <v>2</v>
@@ -4910,7 +4916,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B10" s="19"/>
       <c r="C10" s="20" t="s">
         <v>0</v>
@@ -4925,7 +4931,7 @@
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="21"/>
       <c r="C11" s="20" t="s">
         <v>1</v>
@@ -4940,7 +4946,7 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="7"/>
@@ -4950,14 +4956,14 @@
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
     </row>
-    <row r="14" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -4968,7 +4974,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -4979,7 +4985,7 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -4990,7 +4996,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -5001,7 +5007,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -5012,7 +5018,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -5023,7 +5029,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -5034,7 +5040,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -5045,7 +5051,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -5056,7 +5062,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -5067,7 +5073,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -5078,7 +5084,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -5089,7 +5095,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -5100,7 +5106,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -5111,7 +5117,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -5122,7 +5128,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -5133,7 +5139,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -5144,7 +5150,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -5155,7 +5161,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -5166,7 +5172,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -5177,7 +5183,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -5239,37 +5245,37 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R135"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="13" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="14" max="15" width="9.15234375" style="29" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.1328125" style="29" hidden="1" customWidth="1"/>
     <col min="16" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D2" s="22"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="24" t="s">
         <v>226</v>
       </c>
@@ -5277,7 +5283,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>227</v>
@@ -5285,7 +5291,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>16</v>
@@ -5293,13 +5299,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="26" t="s">
         <v>227</v>
       </c>
@@ -5307,7 +5313,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>7</v>
@@ -5322,7 +5328,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -5336,7 +5342,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -5350,7 +5356,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -5364,7 +5370,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -5378,7 +5384,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -5392,7 +5398,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -5406,7 +5412,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -5420,7 +5426,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -5434,7 +5440,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -5448,7 +5454,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -5462,7 +5468,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -5476,7 +5482,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -5490,7 +5496,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -5504,7 +5510,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -5518,7 +5524,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -5532,7 +5538,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -5546,7 +5552,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -5560,7 +5566,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -5574,7 +5580,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -5588,7 +5594,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -5602,7 +5608,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -5616,7 +5622,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -5630,7 +5636,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -5644,7 +5650,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -5658,7 +5664,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -5672,7 +5678,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -5686,7 +5692,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -5700,7 +5706,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -5714,7 +5720,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -5728,7 +5734,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -5742,7 +5748,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -5756,7 +5762,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -5770,7 +5776,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -5784,7 +5790,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -5798,7 +5804,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -5812,7 +5818,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -5826,7 +5832,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -5840,7 +5846,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -5854,7 +5860,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -5868,7 +5874,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -5882,7 +5888,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -5896,7 +5902,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -5910,7 +5916,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -5924,7 +5930,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -5938,7 +5944,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -5952,7 +5958,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -5966,7 +5972,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -5980,12 +5986,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="33" t="s">
         <v>7</v>
       </c>
@@ -5999,7 +6005,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="35">
         <v>1</v>
       </c>
@@ -6013,7 +6019,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="38">
         <v>2</v>
       </c>
@@ -6027,7 +6033,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="35">
         <v>3</v>
       </c>
@@ -6041,7 +6047,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="38">
         <v>4</v>
       </c>
@@ -6055,7 +6061,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="35">
         <v>5</v>
       </c>
@@ -6069,7 +6075,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C64" s="38">
         <v>6</v>
       </c>
@@ -6083,7 +6089,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C65" s="35">
         <v>7</v>
       </c>
@@ -6097,7 +6103,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C66" s="38">
         <v>8</v>
       </c>
@@ -6111,7 +6117,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C67" s="35">
         <v>9</v>
       </c>
@@ -6125,7 +6131,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C68" s="38">
         <v>10</v>
       </c>
@@ -6139,7 +6145,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C69" s="35">
         <v>11</v>
       </c>
@@ -6153,7 +6159,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C70" s="38">
         <v>12</v>
       </c>
@@ -6167,7 +6173,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C71" s="35">
         <v>13</v>
       </c>
@@ -6181,7 +6187,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C72" s="38">
         <v>14</v>
       </c>
@@ -6195,7 +6201,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C73" s="35">
         <v>15</v>
       </c>
@@ -6209,7 +6215,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C74" s="38">
         <v>16</v>
       </c>
@@ -6223,7 +6229,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C75" s="35">
         <v>17</v>
       </c>
@@ -6237,7 +6243,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C76" s="38">
         <v>18</v>
       </c>
@@ -6251,7 +6257,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C77" s="35">
         <v>19</v>
       </c>
@@ -6265,7 +6271,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C78" s="38">
         <v>20</v>
       </c>
@@ -6279,7 +6285,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C79" s="35">
         <v>21</v>
       </c>
@@ -6293,7 +6299,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C80" s="38">
         <v>22</v>
       </c>
@@ -6307,7 +6313,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C81" s="35">
         <v>23</v>
       </c>
@@ -6321,7 +6327,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C82" s="38">
         <v>24</v>
       </c>
@@ -6335,7 +6341,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C83" s="35">
         <v>25</v>
       </c>
@@ -6349,7 +6355,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C84" s="38">
         <v>26</v>
       </c>
@@ -6363,7 +6369,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C85" s="35">
         <v>27</v>
       </c>
@@ -6377,7 +6383,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C86" s="38">
         <v>28</v>
       </c>
@@ -6391,7 +6397,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C87" s="35">
         <v>29</v>
       </c>
@@ -6405,7 +6411,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C88" s="38">
         <v>30</v>
       </c>
@@ -6419,7 +6425,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C89" s="35">
         <v>31</v>
       </c>
@@ -6433,7 +6439,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C90" s="38">
         <v>32</v>
       </c>
@@ -6447,7 +6453,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C91" s="35">
         <v>33</v>
       </c>
@@ -6461,7 +6467,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C92" s="38">
         <v>34</v>
       </c>
@@ -6475,7 +6481,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C93" s="35">
         <v>35</v>
       </c>
@@ -6489,7 +6495,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C94" s="38">
         <v>36</v>
       </c>
@@ -6503,7 +6509,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C95" s="35">
         <v>37</v>
       </c>
@@ -6517,7 +6523,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C96" s="38">
         <v>38</v>
       </c>
@@ -6531,7 +6537,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C97" s="35">
         <v>39</v>
       </c>
@@ -6545,7 +6551,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C98" s="38">
         <v>40</v>
       </c>
@@ -6559,7 +6565,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C99" s="35">
         <v>41</v>
       </c>
@@ -6573,7 +6579,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C100" s="38">
         <v>42</v>
       </c>
@@ -6587,7 +6593,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C101" s="35">
         <v>43</v>
       </c>
@@ -6601,7 +6607,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C102" s="38">
         <v>44</v>
       </c>
@@ -6615,7 +6621,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C103" s="35">
         <v>45</v>
       </c>
@@ -6629,7 +6635,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C104" s="38">
         <v>46</v>
       </c>
@@ -6643,7 +6649,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C105" s="35">
         <v>47</v>
       </c>
@@ -6657,7 +6663,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C106" s="38">
         <v>48</v>
       </c>
@@ -6671,7 +6677,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C107" s="35">
         <v>49</v>
       </c>
@@ -6685,7 +6691,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C108" s="38">
         <v>50</v>
       </c>
@@ -6699,7 +6705,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C109" s="35">
         <v>51</v>
       </c>
@@ -6713,7 +6719,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C110" s="38">
         <v>52</v>
       </c>
@@ -6727,7 +6733,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C111" s="35">
         <v>53</v>
       </c>
@@ -6741,7 +6747,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C112" s="38">
         <v>54</v>
       </c>
@@ -6755,7 +6761,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C113" s="35">
         <v>55</v>
       </c>
@@ -6769,7 +6775,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C114" s="38">
         <v>56</v>
       </c>
@@ -6783,7 +6789,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C115" s="35">
         <v>57</v>
       </c>
@@ -6797,7 +6803,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C116" s="38">
         <v>58</v>
       </c>
@@ -6811,7 +6817,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C117" s="35">
         <v>59</v>
       </c>
@@ -6825,7 +6831,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C118" s="38">
         <v>60</v>
       </c>
@@ -6839,7 +6845,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C119" s="35">
         <v>61</v>
       </c>
@@ -6853,7 +6859,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C120" s="38">
         <v>62</v>
       </c>
@@ -6867,7 +6873,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C121" s="35">
         <v>63</v>
       </c>
@@ -6881,7 +6887,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C122" s="38">
         <v>64</v>
       </c>
@@ -6895,7 +6901,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C123" s="35">
         <v>65</v>
       </c>
@@ -6909,7 +6915,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C124" s="38">
         <v>66</v>
       </c>
@@ -6923,7 +6929,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C125" s="35">
         <v>67</v>
       </c>
@@ -6937,7 +6943,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C126" s="38">
         <v>68</v>
       </c>
@@ -6951,7 +6957,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C127" s="35">
         <v>69</v>
       </c>
@@ -6965,7 +6971,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C128" s="38">
         <v>70</v>
       </c>
@@ -6979,7 +6985,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C129" s="35">
         <v>71</v>
       </c>
@@ -6993,7 +6999,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C130" s="38">
         <v>72</v>
       </c>
@@ -7007,7 +7013,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C131" s="35">
         <v>73</v>
       </c>
@@ -7021,7 +7027,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C132" s="38">
         <v>74</v>
       </c>
@@ -7035,7 +7041,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="35">
         <v>75</v>
       </c>
@@ -7049,7 +7055,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="38">
         <v>76</v>
       </c>
@@ -7063,7 +7069,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="3">
         <v>77</v>
       </c>
@@ -7100,37 +7106,37 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R135"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="13" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="14" max="15" width="9.15234375" style="29" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.1328125" style="29" hidden="1" customWidth="1"/>
     <col min="16" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D2" s="22"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="24" t="s">
         <v>226</v>
       </c>
@@ -7138,7 +7144,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>227</v>
@@ -7146,7 +7152,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>16</v>
@@ -7154,13 +7160,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="26" t="s">
         <v>227</v>
       </c>
@@ -7168,7 +7174,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>7</v>
@@ -7183,7 +7189,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -7197,7 +7203,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -7211,7 +7217,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -7225,7 +7231,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -7239,7 +7245,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -7253,7 +7259,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -7267,7 +7273,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -7281,7 +7287,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -7295,7 +7301,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -7309,7 +7315,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -7323,7 +7329,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -7337,7 +7343,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -7351,7 +7357,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -7365,7 +7371,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -7379,7 +7385,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -7393,7 +7399,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -7407,7 +7413,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -7421,7 +7427,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -7435,7 +7441,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -7449,7 +7455,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -7463,7 +7469,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -7477,7 +7483,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -7491,7 +7497,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -7505,7 +7511,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -7519,7 +7525,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -7533,7 +7539,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -7547,7 +7553,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -7561,7 +7567,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -7575,7 +7581,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -7589,7 +7595,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -7603,7 +7609,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -7617,7 +7623,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -7631,7 +7637,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -7645,7 +7651,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -7659,7 +7665,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -7673,7 +7679,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -7687,7 +7693,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -7701,7 +7707,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -7715,7 +7721,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -7729,7 +7735,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -7743,7 +7749,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -7757,7 +7763,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -7771,7 +7777,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -7785,7 +7791,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -7799,7 +7805,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -7813,7 +7819,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -7827,7 +7833,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="55" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -7841,12 +7847,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="33" t="s">
         <v>7</v>
       </c>
@@ -7860,7 +7866,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B59" s="41"/>
       <c r="C59" s="37">
         <v>1</v>
@@ -7875,7 +7881,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B60" s="41"/>
       <c r="C60" s="40">
         <v>2</v>
@@ -7890,7 +7896,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="61" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B61" s="41"/>
       <c r="C61" s="37">
         <v>3</v>
@@ -7905,7 +7911,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B62" s="41"/>
       <c r="C62" s="40">
         <v>4</v>
@@ -7920,7 +7926,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B63" s="41"/>
       <c r="C63" s="37">
         <v>5</v>
@@ -7935,7 +7941,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B64" s="41"/>
       <c r="C64" s="40">
         <v>6</v>
@@ -7950,7 +7956,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="65" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B65" s="41"/>
       <c r="C65" s="37">
         <v>7</v>
@@ -7965,7 +7971,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="66" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B66" s="41"/>
       <c r="C66" s="40">
         <v>8</v>
@@ -7980,7 +7986,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B67" s="41"/>
       <c r="C67" s="37">
         <v>9</v>
@@ -7995,7 +8001,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B68" s="41"/>
       <c r="C68" s="40">
         <v>10</v>
@@ -8010,7 +8016,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="69" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B69" s="41"/>
       <c r="C69" s="37">
         <v>11</v>
@@ -8025,7 +8031,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="70" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B70" s="41"/>
       <c r="C70" s="40">
         <v>12</v>
@@ -8040,7 +8046,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B71" s="41"/>
       <c r="C71" s="37">
         <v>13</v>
@@ -8055,7 +8061,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="72" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B72" s="41"/>
       <c r="C72" s="40">
         <v>14</v>
@@ -8070,7 +8076,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="73" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B73" s="41"/>
       <c r="C73" s="37">
         <v>15</v>
@@ -8085,7 +8091,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="74" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B74" s="41"/>
       <c r="C74" s="40">
         <v>16</v>
@@ -8100,7 +8106,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="75" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B75" s="41"/>
       <c r="C75" s="37">
         <v>17</v>
@@ -8115,7 +8121,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="76" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B76" s="41"/>
       <c r="C76" s="40">
         <v>18</v>
@@ -8130,7 +8136,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="77" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B77" s="41"/>
       <c r="C77" s="37">
         <v>19</v>
@@ -8145,7 +8151,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C78" s="38">
         <v>20</v>
       </c>
@@ -8159,7 +8165,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C79" s="35">
         <v>21</v>
       </c>
@@ -8173,7 +8179,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="80" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C80" s="38">
         <v>22</v>
       </c>
@@ -8187,7 +8193,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C81" s="35">
         <v>23</v>
       </c>
@@ -8201,7 +8207,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C82" s="38">
         <v>24</v>
       </c>
@@ -8215,7 +8221,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C83" s="35">
         <v>25</v>
       </c>
@@ -8229,7 +8235,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C84" s="38">
         <v>26</v>
       </c>
@@ -8243,7 +8249,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C85" s="35">
         <v>27</v>
       </c>
@@ -8257,7 +8263,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C86" s="38">
         <v>28</v>
       </c>
@@ -8271,7 +8277,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C87" s="35">
         <v>29</v>
       </c>
@@ -8285,7 +8291,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C88" s="38">
         <v>30</v>
       </c>
@@ -8299,7 +8305,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C89" s="35">
         <v>31</v>
       </c>
@@ -8313,7 +8319,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C90" s="38">
         <v>32</v>
       </c>
@@ -8327,7 +8333,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C91" s="35">
         <v>33</v>
       </c>
@@ -8341,7 +8347,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C92" s="38">
         <v>34</v>
       </c>
@@ -8355,7 +8361,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C93" s="35">
         <v>35</v>
       </c>
@@ -8369,7 +8375,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C94" s="38">
         <v>36</v>
       </c>
@@ -8383,7 +8389,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C95" s="35">
         <v>37</v>
       </c>
@@ -8397,7 +8403,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C96" s="38">
         <v>38</v>
       </c>
@@ -8411,7 +8417,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C97" s="35">
         <v>39</v>
       </c>
@@ -8425,7 +8431,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C98" s="38">
         <v>40</v>
       </c>
@@ -8439,7 +8445,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C99" s="35">
         <v>41</v>
       </c>
@@ -8453,7 +8459,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C100" s="38">
         <v>42</v>
       </c>
@@ -8467,7 +8473,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C101" s="35">
         <v>43</v>
       </c>
@@ -8481,7 +8487,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C102" s="38">
         <v>44</v>
       </c>
@@ -8495,7 +8501,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C103" s="35">
         <v>45</v>
       </c>
@@ -8509,7 +8515,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C104" s="38">
         <v>46</v>
       </c>
@@ -8523,7 +8529,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C105" s="35">
         <v>47</v>
       </c>
@@ -8537,7 +8543,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C106" s="38">
         <v>48</v>
       </c>
@@ -8551,7 +8557,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C107" s="35">
         <v>49</v>
       </c>
@@ -8565,7 +8571,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C108" s="38">
         <v>50</v>
       </c>
@@ -8579,7 +8585,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C109" s="35">
         <v>51</v>
       </c>
@@ -8593,7 +8599,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C110" s="38">
         <v>52</v>
       </c>
@@ -8607,7 +8613,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C111" s="35">
         <v>53</v>
       </c>
@@ -8621,7 +8627,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C112" s="38">
         <v>54</v>
       </c>
@@ -8635,7 +8641,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C113" s="35">
         <v>55</v>
       </c>
@@ -8649,7 +8655,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C114" s="38">
         <v>56</v>
       </c>
@@ -8663,7 +8669,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C115" s="35">
         <v>57</v>
       </c>
@@ -8677,7 +8683,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C116" s="38">
         <v>58</v>
       </c>
@@ -8691,7 +8697,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C117" s="35">
         <v>59</v>
       </c>
@@ -8705,7 +8711,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C118" s="38">
         <v>60</v>
       </c>
@@ -8719,7 +8725,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C119" s="35">
         <v>61</v>
       </c>
@@ -8733,7 +8739,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C120" s="38">
         <v>62</v>
       </c>
@@ -8747,7 +8753,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C121" s="35">
         <v>63</v>
       </c>
@@ -8761,7 +8767,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C122" s="38">
         <v>64</v>
       </c>
@@ -8775,7 +8781,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C123" s="35">
         <v>65</v>
       </c>
@@ -8789,7 +8795,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C124" s="38">
         <v>66</v>
       </c>
@@ -8803,7 +8809,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C125" s="35">
         <v>67</v>
       </c>
@@ -8817,7 +8823,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C126" s="38">
         <v>68</v>
       </c>
@@ -8831,7 +8837,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C127" s="35">
         <v>69</v>
       </c>
@@ -8845,7 +8851,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C128" s="38">
         <v>70</v>
       </c>
@@ -8859,7 +8865,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C129" s="35">
         <v>71</v>
       </c>
@@ -8873,7 +8879,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C130" s="38">
         <v>72</v>
       </c>
@@ -8887,7 +8893,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C131" s="35">
         <v>73</v>
       </c>
@@ -8901,7 +8907,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C132" s="38">
         <v>74</v>
       </c>
@@ -8915,7 +8921,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="35">
         <v>75</v>
       </c>
@@ -8929,7 +8935,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="38">
         <v>76</v>
       </c>
@@ -8943,7 +8949,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="3">
         <v>77</v>
       </c>
@@ -8980,37 +8986,37 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R136"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="29" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="29" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D2" s="22"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="24" t="s">
         <v>226</v>
       </c>
@@ -9018,7 +9024,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>227</v>
@@ -9026,7 +9032,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>16</v>
@@ -9034,13 +9040,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="26" t="s">
         <v>227</v>
       </c>
@@ -9048,7 +9054,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>7</v>
@@ -9063,7 +9069,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -9077,7 +9083,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -9091,7 +9097,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -9105,7 +9111,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -9119,7 +9125,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -9133,7 +9139,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -9147,7 +9153,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -9161,7 +9167,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -9175,7 +9181,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -9189,7 +9195,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -9203,7 +9209,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -9217,7 +9223,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -9231,7 +9237,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -9245,7 +9251,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -9259,7 +9265,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -9273,7 +9279,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -9287,7 +9293,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -9301,7 +9307,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -9315,7 +9321,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -9329,7 +9335,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -9343,7 +9349,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -9357,7 +9363,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -9371,7 +9377,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -9385,7 +9391,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -9399,7 +9405,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -9413,7 +9419,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -9427,7 +9433,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -9441,7 +9447,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -9455,7 +9461,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -9469,7 +9475,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -9483,7 +9489,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -9497,7 +9503,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -9511,7 +9517,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -9525,7 +9531,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -9539,7 +9545,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -9553,7 +9559,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -9567,7 +9573,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -9581,7 +9587,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -9595,7 +9601,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -9609,7 +9615,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -9623,7 +9629,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -9637,7 +9643,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -9651,7 +9657,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -9665,7 +9671,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -9679,7 +9685,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -9693,7 +9699,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -9707,12 +9713,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="33" t="s">
         <v>7</v>
       </c>
@@ -9726,7 +9732,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="35">
         <v>1</v>
       </c>
@@ -9740,7 +9746,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="38">
         <v>2</v>
       </c>
@@ -9754,7 +9760,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="35">
         <v>3</v>
       </c>
@@ -9768,7 +9774,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="38">
         <v>4</v>
       </c>
@@ -9782,7 +9788,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="35">
         <v>5</v>
       </c>
@@ -9796,7 +9802,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="38">
         <v>6</v>
       </c>
@@ -9810,7 +9816,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="29"/>
       <c r="B64" s="27"/>
       <c r="C64" s="35">
@@ -9831,7 +9837,7 @@
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
     </row>
-    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="29"/>
       <c r="B65" s="27"/>
       <c r="C65" s="38">
@@ -9852,7 +9858,7 @@
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
     </row>
-    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="29"/>
       <c r="B66" s="27"/>
       <c r="C66" s="35">
@@ -9873,7 +9879,7 @@
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
     </row>
-    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="29"/>
       <c r="B67" s="27"/>
       <c r="C67" s="38">
@@ -9894,7 +9900,7 @@
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
     </row>
-    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="29"/>
       <c r="B68" s="27"/>
       <c r="C68" s="35">
@@ -9915,7 +9921,7 @@
       <c r="J68" s="29"/>
       <c r="K68" s="29"/>
     </row>
-    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="29"/>
       <c r="B69" s="27"/>
       <c r="C69" s="38">
@@ -9936,7 +9942,7 @@
       <c r="J69" s="29"/>
       <c r="K69" s="29"/>
     </row>
-    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="29"/>
       <c r="B70" s="27"/>
       <c r="C70" s="35">
@@ -9957,7 +9963,7 @@
       <c r="J70" s="29"/>
       <c r="K70" s="29"/>
     </row>
-    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="29"/>
       <c r="B71" s="27"/>
       <c r="C71" s="38">
@@ -9978,7 +9984,7 @@
       <c r="J71" s="29"/>
       <c r="K71" s="29"/>
     </row>
-    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="29"/>
       <c r="B72" s="27"/>
       <c r="C72" s="35">
@@ -9999,7 +10005,7 @@
       <c r="J72" s="29"/>
       <c r="K72" s="29"/>
     </row>
-    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="29"/>
       <c r="B73" s="27"/>
       <c r="C73" s="38">
@@ -10020,7 +10026,7 @@
       <c r="J73" s="29"/>
       <c r="K73" s="29"/>
     </row>
-    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="29"/>
       <c r="B74" s="27"/>
       <c r="C74" s="35">
@@ -10041,7 +10047,7 @@
       <c r="J74" s="29"/>
       <c r="K74" s="29"/>
     </row>
-    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="29"/>
       <c r="B75" s="27"/>
       <c r="C75" s="38">
@@ -10062,7 +10068,7 @@
       <c r="J75" s="29"/>
       <c r="K75" s="29"/>
     </row>
-    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="29"/>
       <c r="B76" s="27"/>
       <c r="C76" s="35">
@@ -10083,7 +10089,7 @@
       <c r="J76" s="29"/>
       <c r="K76" s="29"/>
     </row>
-    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="29"/>
       <c r="B77" s="27"/>
       <c r="C77" s="38">
@@ -10104,7 +10110,7 @@
       <c r="J77" s="29"/>
       <c r="K77" s="29"/>
     </row>
-    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="29"/>
       <c r="B78" s="27"/>
       <c r="C78" s="35">
@@ -10125,7 +10131,7 @@
       <c r="J78" s="29"/>
       <c r="K78" s="29"/>
     </row>
-    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="29"/>
       <c r="B79" s="27"/>
       <c r="C79" s="38">
@@ -10146,7 +10152,7 @@
       <c r="J79" s="29"/>
       <c r="K79" s="29"/>
     </row>
-    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="29"/>
       <c r="B80" s="27"/>
       <c r="C80" s="35">
@@ -10167,7 +10173,7 @@
       <c r="J80" s="29"/>
       <c r="K80" s="29"/>
     </row>
-    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="29"/>
       <c r="B81" s="27"/>
       <c r="C81" s="38">
@@ -10188,7 +10194,7 @@
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
     </row>
-    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="29"/>
       <c r="B82" s="27"/>
       <c r="C82" s="35">
@@ -10209,7 +10215,7 @@
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
     </row>
-    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="29"/>
       <c r="B83" s="27"/>
       <c r="C83" s="38">
@@ -10230,7 +10236,7 @@
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
     </row>
-    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="29"/>
       <c r="B84" s="27"/>
       <c r="C84" s="35">
@@ -10251,7 +10257,7 @@
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
     </row>
-    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="29"/>
       <c r="B85" s="27"/>
       <c r="C85" s="38">
@@ -10272,7 +10278,7 @@
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
     </row>
-    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="29"/>
       <c r="B86" s="27"/>
       <c r="C86" s="35">
@@ -10293,7 +10299,7 @@
       <c r="J86" s="29"/>
       <c r="K86" s="29"/>
     </row>
-    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="29"/>
       <c r="B87" s="27"/>
       <c r="C87" s="38">
@@ -10314,7 +10320,7 @@
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
     </row>
-    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="29"/>
       <c r="B88" s="27"/>
       <c r="C88" s="35">
@@ -10335,7 +10341,7 @@
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
     </row>
-    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="29"/>
       <c r="B89" s="27"/>
       <c r="C89" s="38">
@@ -10356,7 +10362,7 @@
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
     </row>
-    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="29"/>
       <c r="B90" s="27"/>
       <c r="C90" s="35">
@@ -10377,7 +10383,7 @@
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
     </row>
-    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="29"/>
       <c r="B91" s="27"/>
       <c r="C91" s="38">
@@ -10398,7 +10404,7 @@
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
     </row>
-    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="29"/>
       <c r="B92" s="27"/>
       <c r="C92" s="35">
@@ -10419,7 +10425,7 @@
       <c r="J92" s="29"/>
       <c r="K92" s="29"/>
     </row>
-    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="29"/>
       <c r="B93" s="27"/>
       <c r="C93" s="38">
@@ -10440,7 +10446,7 @@
       <c r="J93" s="29"/>
       <c r="K93" s="29"/>
     </row>
-    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="29"/>
       <c r="B94" s="27"/>
       <c r="C94" s="35">
@@ -10461,7 +10467,7 @@
       <c r="J94" s="29"/>
       <c r="K94" s="29"/>
     </row>
-    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="29"/>
       <c r="B95" s="27"/>
       <c r="C95" s="38">
@@ -10482,7 +10488,7 @@
       <c r="J95" s="29"/>
       <c r="K95" s="29"/>
     </row>
-    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="29"/>
       <c r="B96" s="27"/>
       <c r="C96" s="35">
@@ -10503,7 +10509,7 @@
       <c r="J96" s="29"/>
       <c r="K96" s="29"/>
     </row>
-    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="29"/>
       <c r="B97" s="27"/>
       <c r="C97" s="38">
@@ -10524,7 +10530,7 @@
       <c r="J97" s="29"/>
       <c r="K97" s="29"/>
     </row>
-    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="29"/>
       <c r="B98" s="27"/>
       <c r="C98" s="35">
@@ -10545,7 +10551,7 @@
       <c r="J98" s="29"/>
       <c r="K98" s="29"/>
     </row>
-    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="29"/>
       <c r="B99" s="27"/>
       <c r="C99" s="38">
@@ -10566,7 +10572,7 @@
       <c r="J99" s="29"/>
       <c r="K99" s="29"/>
     </row>
-    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="29"/>
       <c r="B100" s="27"/>
       <c r="C100" s="35">
@@ -10587,7 +10593,7 @@
       <c r="J100" s="29"/>
       <c r="K100" s="29"/>
     </row>
-    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="29"/>
       <c r="B101" s="27"/>
       <c r="C101" s="38">
@@ -10608,7 +10614,7 @@
       <c r="J101" s="29"/>
       <c r="K101" s="29"/>
     </row>
-    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="29"/>
       <c r="B102" s="27"/>
       <c r="C102" s="35">
@@ -10629,7 +10635,7 @@
       <c r="J102" s="29"/>
       <c r="K102" s="29"/>
     </row>
-    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="29"/>
       <c r="B103" s="27"/>
       <c r="C103" s="38">
@@ -10650,7 +10656,7 @@
       <c r="J103" s="29"/>
       <c r="K103" s="29"/>
     </row>
-    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="29"/>
       <c r="B104" s="27"/>
       <c r="C104" s="35">
@@ -10671,7 +10677,7 @@
       <c r="J104" s="29"/>
       <c r="K104" s="29"/>
     </row>
-    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="29"/>
       <c r="B105" s="27"/>
       <c r="C105" s="38">
@@ -10692,7 +10698,7 @@
       <c r="J105" s="29"/>
       <c r="K105" s="29"/>
     </row>
-    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="29"/>
       <c r="B106" s="27"/>
       <c r="C106" s="35">
@@ -10713,7 +10719,7 @@
       <c r="J106" s="29"/>
       <c r="K106" s="29"/>
     </row>
-    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="29"/>
       <c r="B107" s="27"/>
       <c r="C107" s="38">
@@ -10734,7 +10740,7 @@
       <c r="J107" s="29"/>
       <c r="K107" s="29"/>
     </row>
-    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="29"/>
       <c r="B108" s="27"/>
       <c r="C108" s="35">
@@ -10755,7 +10761,7 @@
       <c r="J108" s="29"/>
       <c r="K108" s="29"/>
     </row>
-    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="29"/>
       <c r="B109" s="27"/>
       <c r="C109" s="38">
@@ -10776,7 +10782,7 @@
       <c r="J109" s="29"/>
       <c r="K109" s="29"/>
     </row>
-    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="29"/>
       <c r="B110" s="27"/>
       <c r="C110" s="35">
@@ -10797,7 +10803,7 @@
       <c r="J110" s="29"/>
       <c r="K110" s="29"/>
     </row>
-    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="29"/>
       <c r="B111" s="27"/>
       <c r="C111" s="38">
@@ -10818,7 +10824,7 @@
       <c r="J111" s="29"/>
       <c r="K111" s="29"/>
     </row>
-    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="29"/>
       <c r="B112" s="27"/>
       <c r="C112" s="35">
@@ -10839,7 +10845,7 @@
       <c r="J112" s="29"/>
       <c r="K112" s="29"/>
     </row>
-    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="29"/>
       <c r="B113" s="27"/>
       <c r="C113" s="38">
@@ -10860,7 +10866,7 @@
       <c r="J113" s="29"/>
       <c r="K113" s="29"/>
     </row>
-    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="29"/>
       <c r="B114" s="27"/>
       <c r="C114" s="35">
@@ -10881,7 +10887,7 @@
       <c r="J114" s="29"/>
       <c r="K114" s="29"/>
     </row>
-    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="29"/>
       <c r="B115" s="27"/>
       <c r="C115" s="38">
@@ -10902,7 +10908,7 @@
       <c r="J115" s="29"/>
       <c r="K115" s="29"/>
     </row>
-    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="29"/>
       <c r="B116" s="27"/>
       <c r="C116" s="35">
@@ -10923,7 +10929,7 @@
       <c r="J116" s="29"/>
       <c r="K116" s="29"/>
     </row>
-    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="29"/>
       <c r="B117" s="27"/>
       <c r="C117" s="38">
@@ -10944,7 +10950,7 @@
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
     </row>
-    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="29"/>
       <c r="B118" s="27"/>
       <c r="C118" s="35">
@@ -10965,7 +10971,7 @@
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
     </row>
-    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="29"/>
       <c r="B119" s="27"/>
       <c r="C119" s="38">
@@ -10986,7 +10992,7 @@
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
     </row>
-    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="29"/>
       <c r="B120" s="27"/>
       <c r="C120" s="35">
@@ -11007,7 +11013,7 @@
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
     </row>
-    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="29"/>
       <c r="B121" s="27"/>
       <c r="C121" s="38">
@@ -11028,7 +11034,7 @@
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
     </row>
-    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="29"/>
       <c r="B122" s="27"/>
       <c r="C122" s="35">
@@ -11049,7 +11055,7 @@
       <c r="J122" s="29"/>
       <c r="K122" s="29"/>
     </row>
-    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="29"/>
       <c r="B123" s="27"/>
       <c r="C123" s="38">
@@ -11070,7 +11076,7 @@
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
     </row>
-    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="29"/>
       <c r="B124" s="27"/>
       <c r="C124" s="35">
@@ -11091,7 +11097,7 @@
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
     </row>
-    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="29"/>
       <c r="B125" s="27"/>
       <c r="C125" s="38">
@@ -11112,7 +11118,7 @@
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
     </row>
-    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="29"/>
       <c r="B126" s="27"/>
       <c r="C126" s="35">
@@ -11133,7 +11139,7 @@
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
     </row>
-    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="29"/>
       <c r="B127" s="27"/>
       <c r="C127" s="38">
@@ -11154,7 +11160,7 @@
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
     </row>
-    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="29"/>
       <c r="B128" s="27"/>
       <c r="C128" s="35">
@@ -11175,7 +11181,7 @@
       <c r="J128" s="29"/>
       <c r="K128" s="29"/>
     </row>
-    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="29"/>
       <c r="B129" s="27"/>
       <c r="C129" s="38">
@@ -11196,7 +11202,7 @@
       <c r="J129" s="29"/>
       <c r="K129" s="29"/>
     </row>
-    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="29"/>
       <c r="B130" s="27"/>
       <c r="C130" s="35">
@@ -11217,7 +11223,7 @@
       <c r="J130" s="29"/>
       <c r="K130" s="29"/>
     </row>
-    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="29"/>
       <c r="B131" s="27"/>
       <c r="C131" s="38">
@@ -11238,7 +11244,7 @@
       <c r="J131" s="29"/>
       <c r="K131" s="29"/>
     </row>
-    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="29"/>
       <c r="B132" s="27"/>
       <c r="C132" s="35">
@@ -11259,7 +11265,7 @@
       <c r="J132" s="29"/>
       <c r="K132" s="29"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="38">
         <v>76</v>
       </c>
@@ -11273,7 +11279,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="35">
         <v>77</v>
       </c>
@@ -11287,7 +11293,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="38">
         <v>78</v>
       </c>
@@ -11301,7 +11307,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C136" s="3">
         <v>79</v>
       </c>
@@ -11338,37 +11344,37 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R136"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="29" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="29" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D2" s="22"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="24" t="s">
         <v>226</v>
       </c>
@@ -11376,7 +11382,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>227</v>
@@ -11384,7 +11390,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>16</v>
@@ -11392,13 +11398,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="26" t="s">
         <v>227</v>
       </c>
@@ -11406,7 +11412,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>7</v>
@@ -11421,7 +11427,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -11435,7 +11441,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -11449,7 +11455,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -11463,7 +11469,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -11477,7 +11483,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -11491,7 +11497,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -11505,7 +11511,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -11519,7 +11525,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -11533,7 +11539,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -11547,7 +11553,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -11561,7 +11567,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -11575,7 +11581,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -11589,7 +11595,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -11603,7 +11609,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -11617,7 +11623,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -11631,7 +11637,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -11645,7 +11651,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -11659,7 +11665,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -11673,7 +11679,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -11687,7 +11693,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -11701,7 +11707,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -11715,7 +11721,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -11729,7 +11735,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -11743,7 +11749,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -11757,7 +11763,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -11771,7 +11777,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -11785,7 +11791,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -11799,7 +11805,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -11813,7 +11819,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -11827,7 +11833,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -11841,7 +11847,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -11855,7 +11861,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -11869,7 +11875,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -11883,7 +11889,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -11897,7 +11903,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -11911,7 +11917,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -11925,7 +11931,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -11939,7 +11945,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -11953,7 +11959,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -11967,7 +11973,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -11981,7 +11987,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -11995,7 +12001,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -12009,7 +12015,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -12023,7 +12029,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -12037,7 +12043,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -12051,7 +12057,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -12065,12 +12071,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="33" t="s">
         <v>7</v>
       </c>
@@ -12084,7 +12090,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="35">
         <v>1</v>
       </c>
@@ -12098,7 +12104,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="38">
         <v>2</v>
       </c>
@@ -12112,7 +12118,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="35">
         <v>3</v>
       </c>
@@ -12126,7 +12132,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="38">
         <v>4</v>
       </c>
@@ -12140,7 +12146,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="35">
         <v>5</v>
       </c>
@@ -12154,7 +12160,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="38">
         <v>6</v>
       </c>
@@ -12168,7 +12174,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="29"/>
       <c r="B64" s="27"/>
       <c r="C64" s="35">
@@ -12189,7 +12195,7 @@
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
     </row>
-    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="29"/>
       <c r="B65" s="27"/>
       <c r="C65" s="38">
@@ -12210,7 +12216,7 @@
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
     </row>
-    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="29"/>
       <c r="B66" s="27"/>
       <c r="C66" s="35">
@@ -12231,7 +12237,7 @@
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
     </row>
-    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="29"/>
       <c r="B67" s="27"/>
       <c r="C67" s="38">
@@ -12252,7 +12258,7 @@
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
     </row>
-    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="29"/>
       <c r="B68" s="27"/>
       <c r="C68" s="35">
@@ -12273,7 +12279,7 @@
       <c r="J68" s="29"/>
       <c r="K68" s="29"/>
     </row>
-    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="29"/>
       <c r="B69" s="27"/>
       <c r="C69" s="38">
@@ -12294,7 +12300,7 @@
       <c r="J69" s="29"/>
       <c r="K69" s="29"/>
     </row>
-    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="29"/>
       <c r="B70" s="27"/>
       <c r="C70" s="35">
@@ -12315,7 +12321,7 @@
       <c r="J70" s="29"/>
       <c r="K70" s="29"/>
     </row>
-    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="29"/>
       <c r="B71" s="27"/>
       <c r="C71" s="38">
@@ -12336,7 +12342,7 @@
       <c r="J71" s="29"/>
       <c r="K71" s="29"/>
     </row>
-    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="29"/>
       <c r="B72" s="27"/>
       <c r="C72" s="35">
@@ -12357,7 +12363,7 @@
       <c r="J72" s="29"/>
       <c r="K72" s="29"/>
     </row>
-    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="29"/>
       <c r="B73" s="27"/>
       <c r="C73" s="38">
@@ -12378,7 +12384,7 @@
       <c r="J73" s="29"/>
       <c r="K73" s="29"/>
     </row>
-    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="29"/>
       <c r="B74" s="27"/>
       <c r="C74" s="35">
@@ -12399,7 +12405,7 @@
       <c r="J74" s="29"/>
       <c r="K74" s="29"/>
     </row>
-    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="29"/>
       <c r="B75" s="27"/>
       <c r="C75" s="38">
@@ -12420,7 +12426,7 @@
       <c r="J75" s="29"/>
       <c r="K75" s="29"/>
     </row>
-    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="29"/>
       <c r="B76" s="27"/>
       <c r="C76" s="35">
@@ -12441,7 +12447,7 @@
       <c r="J76" s="29"/>
       <c r="K76" s="29"/>
     </row>
-    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="29"/>
       <c r="B77" s="27"/>
       <c r="C77" s="38">
@@ -12462,7 +12468,7 @@
       <c r="J77" s="29"/>
       <c r="K77" s="29"/>
     </row>
-    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="29"/>
       <c r="B78" s="27"/>
       <c r="C78" s="35">
@@ -12483,7 +12489,7 @@
       <c r="J78" s="29"/>
       <c r="K78" s="29"/>
     </row>
-    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="29"/>
       <c r="B79" s="27"/>
       <c r="C79" s="38">
@@ -12504,7 +12510,7 @@
       <c r="J79" s="29"/>
       <c r="K79" s="29"/>
     </row>
-    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="29"/>
       <c r="B80" s="27"/>
       <c r="C80" s="35">
@@ -12525,7 +12531,7 @@
       <c r="J80" s="29"/>
       <c r="K80" s="29"/>
     </row>
-    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="29"/>
       <c r="B81" s="27"/>
       <c r="C81" s="38">
@@ -12546,7 +12552,7 @@
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
     </row>
-    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="29"/>
       <c r="B82" s="27"/>
       <c r="C82" s="35">
@@ -12567,7 +12573,7 @@
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
     </row>
-    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="29"/>
       <c r="B83" s="27"/>
       <c r="C83" s="38">
@@ -12588,7 +12594,7 @@
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
     </row>
-    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="29"/>
       <c r="B84" s="27"/>
       <c r="C84" s="35">
@@ -12609,7 +12615,7 @@
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
     </row>
-    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="29"/>
       <c r="B85" s="27"/>
       <c r="C85" s="38">
@@ -12630,7 +12636,7 @@
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
     </row>
-    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="29"/>
       <c r="B86" s="27"/>
       <c r="C86" s="35">
@@ -12651,7 +12657,7 @@
       <c r="J86" s="29"/>
       <c r="K86" s="29"/>
     </row>
-    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="29"/>
       <c r="B87" s="27"/>
       <c r="C87" s="38">
@@ -12672,7 +12678,7 @@
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
     </row>
-    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="29"/>
       <c r="B88" s="27"/>
       <c r="C88" s="35">
@@ -12693,7 +12699,7 @@
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
     </row>
-    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="29"/>
       <c r="B89" s="27"/>
       <c r="C89" s="38">
@@ -12714,7 +12720,7 @@
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
     </row>
-    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="29"/>
       <c r="B90" s="27"/>
       <c r="C90" s="35">
@@ -12735,7 +12741,7 @@
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
     </row>
-    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="29"/>
       <c r="B91" s="27"/>
       <c r="C91" s="38">
@@ -12756,7 +12762,7 @@
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
     </row>
-    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="29"/>
       <c r="B92" s="27"/>
       <c r="C92" s="35">
@@ -12777,7 +12783,7 @@
       <c r="J92" s="29"/>
       <c r="K92" s="29"/>
     </row>
-    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="29"/>
       <c r="B93" s="27"/>
       <c r="C93" s="38">
@@ -12798,7 +12804,7 @@
       <c r="J93" s="29"/>
       <c r="K93" s="29"/>
     </row>
-    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="29"/>
       <c r="B94" s="27"/>
       <c r="C94" s="35">
@@ -12819,7 +12825,7 @@
       <c r="J94" s="29"/>
       <c r="K94" s="29"/>
     </row>
-    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="29"/>
       <c r="B95" s="27"/>
       <c r="C95" s="38">
@@ -12840,7 +12846,7 @@
       <c r="J95" s="29"/>
       <c r="K95" s="29"/>
     </row>
-    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="29"/>
       <c r="B96" s="27"/>
       <c r="C96" s="35">
@@ -12861,7 +12867,7 @@
       <c r="J96" s="29"/>
       <c r="K96" s="29"/>
     </row>
-    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="29"/>
       <c r="B97" s="27"/>
       <c r="C97" s="38">
@@ -12882,7 +12888,7 @@
       <c r="J97" s="29"/>
       <c r="K97" s="29"/>
     </row>
-    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="29"/>
       <c r="B98" s="27"/>
       <c r="C98" s="35">
@@ -12903,7 +12909,7 @@
       <c r="J98" s="29"/>
       <c r="K98" s="29"/>
     </row>
-    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="29"/>
       <c r="B99" s="27"/>
       <c r="C99" s="38">
@@ -12924,7 +12930,7 @@
       <c r="J99" s="29"/>
       <c r="K99" s="29"/>
     </row>
-    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="29"/>
       <c r="B100" s="27"/>
       <c r="C100" s="35">
@@ -12945,7 +12951,7 @@
       <c r="J100" s="29"/>
       <c r="K100" s="29"/>
     </row>
-    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="29"/>
       <c r="B101" s="27"/>
       <c r="C101" s="38">
@@ -12966,7 +12972,7 @@
       <c r="J101" s="29"/>
       <c r="K101" s="29"/>
     </row>
-    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="29"/>
       <c r="B102" s="27"/>
       <c r="C102" s="35">
@@ -12987,7 +12993,7 @@
       <c r="J102" s="29"/>
       <c r="K102" s="29"/>
     </row>
-    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="29"/>
       <c r="B103" s="27"/>
       <c r="C103" s="38">
@@ -13008,7 +13014,7 @@
       <c r="J103" s="29"/>
       <c r="K103" s="29"/>
     </row>
-    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="29"/>
       <c r="B104" s="27"/>
       <c r="C104" s="35">
@@ -13029,7 +13035,7 @@
       <c r="J104" s="29"/>
       <c r="K104" s="29"/>
     </row>
-    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="29"/>
       <c r="B105" s="27"/>
       <c r="C105" s="38">
@@ -13050,7 +13056,7 @@
       <c r="J105" s="29"/>
       <c r="K105" s="29"/>
     </row>
-    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="29"/>
       <c r="B106" s="27"/>
       <c r="C106" s="35">
@@ -13071,7 +13077,7 @@
       <c r="J106" s="29"/>
       <c r="K106" s="29"/>
     </row>
-    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="29"/>
       <c r="B107" s="27"/>
       <c r="C107" s="38">
@@ -13092,7 +13098,7 @@
       <c r="J107" s="29"/>
       <c r="K107" s="29"/>
     </row>
-    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="29"/>
       <c r="B108" s="27"/>
       <c r="C108" s="35">
@@ -13113,7 +13119,7 @@
       <c r="J108" s="29"/>
       <c r="K108" s="29"/>
     </row>
-    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="29"/>
       <c r="B109" s="27"/>
       <c r="C109" s="38">
@@ -13134,7 +13140,7 @@
       <c r="J109" s="29"/>
       <c r="K109" s="29"/>
     </row>
-    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="29"/>
       <c r="B110" s="27"/>
       <c r="C110" s="35">
@@ -13155,7 +13161,7 @@
       <c r="J110" s="29"/>
       <c r="K110" s="29"/>
     </row>
-    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="29"/>
       <c r="B111" s="27"/>
       <c r="C111" s="38">
@@ -13176,7 +13182,7 @@
       <c r="J111" s="29"/>
       <c r="K111" s="29"/>
     </row>
-    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="29"/>
       <c r="B112" s="27"/>
       <c r="C112" s="35">
@@ -13197,7 +13203,7 @@
       <c r="J112" s="29"/>
       <c r="K112" s="29"/>
     </row>
-    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="29"/>
       <c r="B113" s="27"/>
       <c r="C113" s="38">
@@ -13218,7 +13224,7 @@
       <c r="J113" s="29"/>
       <c r="K113" s="29"/>
     </row>
-    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="29"/>
       <c r="B114" s="27"/>
       <c r="C114" s="35">
@@ -13239,7 +13245,7 @@
       <c r="J114" s="29"/>
       <c r="K114" s="29"/>
     </row>
-    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="29"/>
       <c r="B115" s="27"/>
       <c r="C115" s="38">
@@ -13260,7 +13266,7 @@
       <c r="J115" s="29"/>
       <c r="K115" s="29"/>
     </row>
-    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="29"/>
       <c r="B116" s="27"/>
       <c r="C116" s="35">
@@ -13281,7 +13287,7 @@
       <c r="J116" s="29"/>
       <c r="K116" s="29"/>
     </row>
-    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="29"/>
       <c r="B117" s="27"/>
       <c r="C117" s="38">
@@ -13302,7 +13308,7 @@
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
     </row>
-    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="29"/>
       <c r="B118" s="27"/>
       <c r="C118" s="35">
@@ -13323,7 +13329,7 @@
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
     </row>
-    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="29"/>
       <c r="B119" s="27"/>
       <c r="C119" s="38">
@@ -13344,7 +13350,7 @@
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
     </row>
-    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="29"/>
       <c r="B120" s="27"/>
       <c r="C120" s="35">
@@ -13365,7 +13371,7 @@
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
     </row>
-    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="29"/>
       <c r="B121" s="27"/>
       <c r="C121" s="38">
@@ -13386,7 +13392,7 @@
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
     </row>
-    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="29"/>
       <c r="B122" s="27"/>
       <c r="C122" s="35">
@@ -13407,7 +13413,7 @@
       <c r="J122" s="29"/>
       <c r="K122" s="29"/>
     </row>
-    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="29"/>
       <c r="B123" s="27"/>
       <c r="C123" s="38">
@@ -13428,7 +13434,7 @@
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
     </row>
-    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="29"/>
       <c r="B124" s="27"/>
       <c r="C124" s="35">
@@ -13449,7 +13455,7 @@
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
     </row>
-    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="29"/>
       <c r="B125" s="27"/>
       <c r="C125" s="38">
@@ -13470,7 +13476,7 @@
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
     </row>
-    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="29"/>
       <c r="B126" s="27"/>
       <c r="C126" s="35">
@@ -13491,7 +13497,7 @@
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
     </row>
-    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="29"/>
       <c r="B127" s="27"/>
       <c r="C127" s="38">
@@ -13512,7 +13518,7 @@
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
     </row>
-    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="29"/>
       <c r="B128" s="27"/>
       <c r="C128" s="35">
@@ -13533,7 +13539,7 @@
       <c r="J128" s="29"/>
       <c r="K128" s="29"/>
     </row>
-    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="29"/>
       <c r="B129" s="27"/>
       <c r="C129" s="38">
@@ -13554,7 +13560,7 @@
       <c r="J129" s="29"/>
       <c r="K129" s="29"/>
     </row>
-    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="29"/>
       <c r="B130" s="27"/>
       <c r="C130" s="35">
@@ -13575,7 +13581,7 @@
       <c r="J130" s="29"/>
       <c r="K130" s="29"/>
     </row>
-    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="29"/>
       <c r="B131" s="27"/>
       <c r="C131" s="38">
@@ -13596,7 +13602,7 @@
       <c r="J131" s="29"/>
       <c r="K131" s="29"/>
     </row>
-    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="29"/>
       <c r="B132" s="27"/>
       <c r="C132" s="35">
@@ -13617,7 +13623,7 @@
       <c r="J132" s="29"/>
       <c r="K132" s="29"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="38">
         <v>76</v>
       </c>
@@ -13631,7 +13637,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="35">
         <v>77</v>
       </c>
@@ -13645,7 +13651,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="38">
         <v>78</v>
       </c>
@@ -13659,7 +13665,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C136" s="3">
         <v>79</v>
       </c>
@@ -13696,37 +13702,37 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R136"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="29" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="29" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D2" s="22"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="24" t="s">
         <v>226</v>
       </c>
@@ -13734,7 +13740,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>227</v>
@@ -13742,7 +13748,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>16</v>
@@ -13750,13 +13756,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="26" t="s">
         <v>227</v>
       </c>
@@ -13764,7 +13770,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>7</v>
@@ -13779,7 +13785,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -13793,7 +13799,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -13807,7 +13813,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -13821,7 +13827,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -13835,7 +13841,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -13849,7 +13855,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -13863,7 +13869,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -13877,7 +13883,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -13891,7 +13897,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -13905,7 +13911,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -13919,7 +13925,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -13933,7 +13939,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -13947,7 +13953,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -13961,7 +13967,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -13975,7 +13981,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -13989,7 +13995,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -14003,7 +14009,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -14017,7 +14023,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -14031,7 +14037,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -14045,7 +14051,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -14059,7 +14065,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -14073,7 +14079,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -14087,7 +14093,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -14101,7 +14107,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -14115,7 +14121,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -14129,7 +14135,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -14143,7 +14149,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -14157,7 +14163,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -14171,7 +14177,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -14185,7 +14191,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -14199,7 +14205,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -14213,7 +14219,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -14227,7 +14233,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -14241,7 +14247,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -14255,7 +14261,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -14269,7 +14275,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -14283,7 +14289,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -14297,7 +14303,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -14311,7 +14317,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -14325,7 +14331,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -14339,7 +14345,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -14353,7 +14359,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -14367,7 +14373,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -14381,7 +14387,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -14395,7 +14401,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -14409,7 +14415,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -14423,12 +14429,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="33" t="s">
         <v>7</v>
       </c>
@@ -14442,7 +14448,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="35">
         <v>1</v>
       </c>
@@ -14456,7 +14462,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="38">
         <v>2</v>
       </c>
@@ -14470,7 +14476,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="35">
         <v>3</v>
       </c>
@@ -14484,7 +14490,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="38">
         <v>4</v>
       </c>
@@ -14498,7 +14504,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="35">
         <v>5</v>
       </c>
@@ -14512,7 +14518,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="38">
         <v>6</v>
       </c>
@@ -14526,7 +14532,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="29"/>
       <c r="B64" s="27"/>
       <c r="C64" s="35">
@@ -14547,7 +14553,7 @@
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
     </row>
-    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="29"/>
       <c r="B65" s="27"/>
       <c r="C65" s="38">
@@ -14568,7 +14574,7 @@
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
     </row>
-    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="29"/>
       <c r="B66" s="27"/>
       <c r="C66" s="35">
@@ -14589,7 +14595,7 @@
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
     </row>
-    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="29"/>
       <c r="B67" s="27"/>
       <c r="C67" s="38">
@@ -14610,7 +14616,7 @@
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
     </row>
-    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="29"/>
       <c r="B68" s="27"/>
       <c r="C68" s="35">
@@ -14631,7 +14637,7 @@
       <c r="J68" s="29"/>
       <c r="K68" s="29"/>
     </row>
-    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="29"/>
       <c r="B69" s="27"/>
       <c r="C69" s="38">
@@ -14652,7 +14658,7 @@
       <c r="J69" s="29"/>
       <c r="K69" s="29"/>
     </row>
-    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="29"/>
       <c r="B70" s="27"/>
       <c r="C70" s="35">
@@ -14673,7 +14679,7 @@
       <c r="J70" s="29"/>
       <c r="K70" s="29"/>
     </row>
-    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="29"/>
       <c r="B71" s="27"/>
       <c r="C71" s="38">
@@ -14694,7 +14700,7 @@
       <c r="J71" s="29"/>
       <c r="K71" s="29"/>
     </row>
-    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="29"/>
       <c r="B72" s="27"/>
       <c r="C72" s="35">
@@ -14715,7 +14721,7 @@
       <c r="J72" s="29"/>
       <c r="K72" s="29"/>
     </row>
-    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="29"/>
       <c r="B73" s="27"/>
       <c r="C73" s="38">
@@ -14736,7 +14742,7 @@
       <c r="J73" s="29"/>
       <c r="K73" s="29"/>
     </row>
-    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="29"/>
       <c r="B74" s="27"/>
       <c r="C74" s="35">
@@ -14757,7 +14763,7 @@
       <c r="J74" s="29"/>
       <c r="K74" s="29"/>
     </row>
-    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="29"/>
       <c r="B75" s="27"/>
       <c r="C75" s="38">
@@ -14778,7 +14784,7 @@
       <c r="J75" s="29"/>
       <c r="K75" s="29"/>
     </row>
-    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="29"/>
       <c r="B76" s="27"/>
       <c r="C76" s="35">
@@ -14799,7 +14805,7 @@
       <c r="J76" s="29"/>
       <c r="K76" s="29"/>
     </row>
-    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="29"/>
       <c r="B77" s="27"/>
       <c r="C77" s="38">
@@ -14820,7 +14826,7 @@
       <c r="J77" s="29"/>
       <c r="K77" s="29"/>
     </row>
-    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="29"/>
       <c r="B78" s="27"/>
       <c r="C78" s="35">
@@ -14841,7 +14847,7 @@
       <c r="J78" s="29"/>
       <c r="K78" s="29"/>
     </row>
-    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="29"/>
       <c r="B79" s="27"/>
       <c r="C79" s="38">
@@ -14862,7 +14868,7 @@
       <c r="J79" s="29"/>
       <c r="K79" s="29"/>
     </row>
-    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="29"/>
       <c r="B80" s="27"/>
       <c r="C80" s="35">
@@ -14883,7 +14889,7 @@
       <c r="J80" s="29"/>
       <c r="K80" s="29"/>
     </row>
-    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="29"/>
       <c r="B81" s="27"/>
       <c r="C81" s="38">
@@ -14904,7 +14910,7 @@
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
     </row>
-    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="29"/>
       <c r="B82" s="27"/>
       <c r="C82" s="35">
@@ -14925,7 +14931,7 @@
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
     </row>
-    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="29"/>
       <c r="B83" s="27"/>
       <c r="C83" s="38">
@@ -14946,7 +14952,7 @@
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
     </row>
-    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="29"/>
       <c r="B84" s="27"/>
       <c r="C84" s="35">
@@ -14967,7 +14973,7 @@
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
     </row>
-    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="29"/>
       <c r="B85" s="27"/>
       <c r="C85" s="38">
@@ -14988,7 +14994,7 @@
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
     </row>
-    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="29"/>
       <c r="B86" s="27"/>
       <c r="C86" s="35">
@@ -15009,7 +15015,7 @@
       <c r="J86" s="29"/>
       <c r="K86" s="29"/>
     </row>
-    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="29"/>
       <c r="B87" s="27"/>
       <c r="C87" s="38">
@@ -15030,7 +15036,7 @@
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
     </row>
-    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="29"/>
       <c r="B88" s="27"/>
       <c r="C88" s="35">
@@ -15051,7 +15057,7 @@
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
     </row>
-    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="29"/>
       <c r="B89" s="27"/>
       <c r="C89" s="38">
@@ -15072,7 +15078,7 @@
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
     </row>
-    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="29"/>
       <c r="B90" s="27"/>
       <c r="C90" s="35">
@@ -15093,7 +15099,7 @@
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
     </row>
-    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="29"/>
       <c r="B91" s="27"/>
       <c r="C91" s="38">
@@ -15114,7 +15120,7 @@
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
     </row>
-    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="29"/>
       <c r="B92" s="27"/>
       <c r="C92" s="35">
@@ -15135,7 +15141,7 @@
       <c r="J92" s="29"/>
       <c r="K92" s="29"/>
     </row>
-    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="29"/>
       <c r="B93" s="27"/>
       <c r="C93" s="38">
@@ -15156,7 +15162,7 @@
       <c r="J93" s="29"/>
       <c r="K93" s="29"/>
     </row>
-    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="29"/>
       <c r="B94" s="27"/>
       <c r="C94" s="35">
@@ -15177,7 +15183,7 @@
       <c r="J94" s="29"/>
       <c r="K94" s="29"/>
     </row>
-    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="29"/>
       <c r="B95" s="27"/>
       <c r="C95" s="38">
@@ -15198,7 +15204,7 @@
       <c r="J95" s="29"/>
       <c r="K95" s="29"/>
     </row>
-    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="29"/>
       <c r="B96" s="27"/>
       <c r="C96" s="35">
@@ -15219,7 +15225,7 @@
       <c r="J96" s="29"/>
       <c r="K96" s="29"/>
     </row>
-    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="29"/>
       <c r="B97" s="27"/>
       <c r="C97" s="38">
@@ -15240,7 +15246,7 @@
       <c r="J97" s="29"/>
       <c r="K97" s="29"/>
     </row>
-    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="29"/>
       <c r="B98" s="27"/>
       <c r="C98" s="35">
@@ -15261,7 +15267,7 @@
       <c r="J98" s="29"/>
       <c r="K98" s="29"/>
     </row>
-    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="29"/>
       <c r="B99" s="27"/>
       <c r="C99" s="38">
@@ -15282,7 +15288,7 @@
       <c r="J99" s="29"/>
       <c r="K99" s="29"/>
     </row>
-    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="29"/>
       <c r="B100" s="27"/>
       <c r="C100" s="35">
@@ -15303,7 +15309,7 @@
       <c r="J100" s="29"/>
       <c r="K100" s="29"/>
     </row>
-    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="29"/>
       <c r="B101" s="27"/>
       <c r="C101" s="38">
@@ -15324,7 +15330,7 @@
       <c r="J101" s="29"/>
       <c r="K101" s="29"/>
     </row>
-    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="29"/>
       <c r="B102" s="27"/>
       <c r="C102" s="35">
@@ -15345,7 +15351,7 @@
       <c r="J102" s="29"/>
       <c r="K102" s="29"/>
     </row>
-    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="29"/>
       <c r="B103" s="27"/>
       <c r="C103" s="38">
@@ -15366,7 +15372,7 @@
       <c r="J103" s="29"/>
       <c r="K103" s="29"/>
     </row>
-    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="29"/>
       <c r="B104" s="27"/>
       <c r="C104" s="35">
@@ -15387,7 +15393,7 @@
       <c r="J104" s="29"/>
       <c r="K104" s="29"/>
     </row>
-    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="29"/>
       <c r="B105" s="27"/>
       <c r="C105" s="38">
@@ -15408,7 +15414,7 @@
       <c r="J105" s="29"/>
       <c r="K105" s="29"/>
     </row>
-    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="29"/>
       <c r="B106" s="27"/>
       <c r="C106" s="35">
@@ -15429,7 +15435,7 @@
       <c r="J106" s="29"/>
       <c r="K106" s="29"/>
     </row>
-    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="29"/>
       <c r="B107" s="27"/>
       <c r="C107" s="38">
@@ -15450,7 +15456,7 @@
       <c r="J107" s="29"/>
       <c r="K107" s="29"/>
     </row>
-    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="29"/>
       <c r="B108" s="27"/>
       <c r="C108" s="35">
@@ -15471,7 +15477,7 @@
       <c r="J108" s="29"/>
       <c r="K108" s="29"/>
     </row>
-    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="29"/>
       <c r="B109" s="27"/>
       <c r="C109" s="38">
@@ -15492,7 +15498,7 @@
       <c r="J109" s="29"/>
       <c r="K109" s="29"/>
     </row>
-    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="29"/>
       <c r="B110" s="27"/>
       <c r="C110" s="35">
@@ -15513,7 +15519,7 @@
       <c r="J110" s="29"/>
       <c r="K110" s="29"/>
     </row>
-    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="29"/>
       <c r="B111" s="27"/>
       <c r="C111" s="38">
@@ -15534,7 +15540,7 @@
       <c r="J111" s="29"/>
       <c r="K111" s="29"/>
     </row>
-    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="29"/>
       <c r="B112" s="27"/>
       <c r="C112" s="35">
@@ -15555,7 +15561,7 @@
       <c r="J112" s="29"/>
       <c r="K112" s="29"/>
     </row>
-    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="29"/>
       <c r="B113" s="27"/>
       <c r="C113" s="38">
@@ -15576,7 +15582,7 @@
       <c r="J113" s="29"/>
       <c r="K113" s="29"/>
     </row>
-    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="29"/>
       <c r="B114" s="27"/>
       <c r="C114" s="35">
@@ -15597,7 +15603,7 @@
       <c r="J114" s="29"/>
       <c r="K114" s="29"/>
     </row>
-    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="29"/>
       <c r="B115" s="27"/>
       <c r="C115" s="38">
@@ -15618,7 +15624,7 @@
       <c r="J115" s="29"/>
       <c r="K115" s="29"/>
     </row>
-    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="29"/>
       <c r="B116" s="27"/>
       <c r="C116" s="35">
@@ -15639,7 +15645,7 @@
       <c r="J116" s="29"/>
       <c r="K116" s="29"/>
     </row>
-    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="29"/>
       <c r="B117" s="27"/>
       <c r="C117" s="38">
@@ -15660,7 +15666,7 @@
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
     </row>
-    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="29"/>
       <c r="B118" s="27"/>
       <c r="C118" s="35">
@@ -15681,7 +15687,7 @@
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
     </row>
-    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="29"/>
       <c r="B119" s="27"/>
       <c r="C119" s="38">
@@ -15702,7 +15708,7 @@
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
     </row>
-    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="29"/>
       <c r="B120" s="27"/>
       <c r="C120" s="35">
@@ -15723,7 +15729,7 @@
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
     </row>
-    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="29"/>
       <c r="B121" s="27"/>
       <c r="C121" s="38">
@@ -15744,7 +15750,7 @@
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
     </row>
-    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="29"/>
       <c r="B122" s="27"/>
       <c r="C122" s="35">
@@ -15765,7 +15771,7 @@
       <c r="J122" s="29"/>
       <c r="K122" s="29"/>
     </row>
-    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="29"/>
       <c r="B123" s="27"/>
       <c r="C123" s="38">
@@ -15786,7 +15792,7 @@
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
     </row>
-    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="29"/>
       <c r="B124" s="27"/>
       <c r="C124" s="35">
@@ -15807,7 +15813,7 @@
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
     </row>
-    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="29"/>
       <c r="B125" s="27"/>
       <c r="C125" s="38">
@@ -15828,7 +15834,7 @@
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
     </row>
-    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="29"/>
       <c r="B126" s="27"/>
       <c r="C126" s="35">
@@ -15849,7 +15855,7 @@
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
     </row>
-    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="29"/>
       <c r="B127" s="27"/>
       <c r="C127" s="38">
@@ -15870,7 +15876,7 @@
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
     </row>
-    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="29"/>
       <c r="B128" s="27"/>
       <c r="C128" s="35">
@@ -15891,7 +15897,7 @@
       <c r="J128" s="29"/>
       <c r="K128" s="29"/>
     </row>
-    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="29"/>
       <c r="B129" s="27"/>
       <c r="C129" s="38">
@@ -15912,7 +15918,7 @@
       <c r="J129" s="29"/>
       <c r="K129" s="29"/>
     </row>
-    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="29"/>
       <c r="B130" s="27"/>
       <c r="C130" s="35">
@@ -15933,7 +15939,7 @@
       <c r="J130" s="29"/>
       <c r="K130" s="29"/>
     </row>
-    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="29"/>
       <c r="B131" s="27"/>
       <c r="C131" s="38">
@@ -15954,7 +15960,7 @@
       <c r="J131" s="29"/>
       <c r="K131" s="29"/>
     </row>
-    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="29"/>
       <c r="B132" s="27"/>
       <c r="C132" s="35">
@@ -15975,7 +15981,7 @@
       <c r="J132" s="29"/>
       <c r="K132" s="29"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="38">
         <v>76</v>
       </c>
@@ -15989,7 +15995,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="35">
         <v>77</v>
       </c>
@@ -16003,7 +16009,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -16017,7 +16023,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C136" s="3">
         <v>79</v>
       </c>
@@ -16054,37 +16060,37 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R136"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="29" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="29" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D2" s="22"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="24" t="s">
         <v>226</v>
       </c>
@@ -16092,7 +16098,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>227</v>
@@ -16100,7 +16106,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>16</v>
@@ -16108,13 +16114,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="26" t="s">
         <v>227</v>
       </c>
@@ -16122,7 +16128,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>7</v>
@@ -16137,7 +16143,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -16151,7 +16157,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -16165,7 +16171,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -16179,7 +16185,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -16193,7 +16199,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -16207,7 +16213,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -16221,7 +16227,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -16235,7 +16241,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -16249,7 +16255,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -16263,7 +16269,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -16277,7 +16283,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -16291,7 +16297,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -16305,7 +16311,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -16319,7 +16325,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -16333,7 +16339,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -16347,7 +16353,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -16361,7 +16367,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -16375,7 +16381,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -16389,7 +16395,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -16403,7 +16409,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -16417,7 +16423,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -16431,7 +16437,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -16445,7 +16451,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -16459,7 +16465,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -16473,7 +16479,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -16487,7 +16493,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -16501,7 +16507,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -16515,7 +16521,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -16529,7 +16535,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -16543,7 +16549,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -16557,7 +16563,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -16571,7 +16577,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -16585,7 +16591,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -16599,7 +16605,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -16613,7 +16619,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -16627,7 +16633,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -16641,7 +16647,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -16655,7 +16661,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -16669,7 +16675,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -16683,7 +16689,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -16697,7 +16703,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -16711,7 +16717,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -16725,7 +16731,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -16739,7 +16745,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -16753,7 +16759,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -16767,7 +16773,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -16781,12 +16787,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="33" t="s">
         <v>7</v>
       </c>
@@ -16800,7 +16806,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="35">
         <v>1</v>
       </c>
@@ -16814,7 +16820,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="38">
         <v>2</v>
       </c>
@@ -16828,7 +16834,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="35">
         <v>3</v>
       </c>
@@ -16842,7 +16848,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="38">
         <v>4</v>
       </c>
@@ -16856,7 +16862,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="35">
         <v>5</v>
       </c>
@@ -16870,7 +16876,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="38">
         <v>6</v>
       </c>
@@ -16884,7 +16890,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="29"/>
       <c r="B64" s="27"/>
       <c r="C64" s="35">
@@ -16905,7 +16911,7 @@
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
     </row>
-    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="29"/>
       <c r="B65" s="27"/>
       <c r="C65" s="38">
@@ -16926,7 +16932,7 @@
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
     </row>
-    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="29"/>
       <c r="B66" s="27"/>
       <c r="C66" s="35">
@@ -16947,7 +16953,7 @@
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
     </row>
-    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="29"/>
       <c r="B67" s="27"/>
       <c r="C67" s="38">
@@ -16968,7 +16974,7 @@
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
     </row>
-    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="29"/>
       <c r="B68" s="27"/>
       <c r="C68" s="35">
@@ -16989,7 +16995,7 @@
       <c r="J68" s="29"/>
       <c r="K68" s="29"/>
     </row>
-    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="29"/>
       <c r="B69" s="27"/>
       <c r="C69" s="38">
@@ -17010,7 +17016,7 @@
       <c r="J69" s="29"/>
       <c r="K69" s="29"/>
     </row>
-    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="29"/>
       <c r="B70" s="27"/>
       <c r="C70" s="35">
@@ -17031,7 +17037,7 @@
       <c r="J70" s="29"/>
       <c r="K70" s="29"/>
     </row>
-    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="29"/>
       <c r="B71" s="27"/>
       <c r="C71" s="38">
@@ -17052,7 +17058,7 @@
       <c r="J71" s="29"/>
       <c r="K71" s="29"/>
     </row>
-    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="29"/>
       <c r="B72" s="27"/>
       <c r="C72" s="35">
@@ -17073,7 +17079,7 @@
       <c r="J72" s="29"/>
       <c r="K72" s="29"/>
     </row>
-    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="29"/>
       <c r="B73" s="27"/>
       <c r="C73" s="38">
@@ -17094,7 +17100,7 @@
       <c r="J73" s="29"/>
       <c r="K73" s="29"/>
     </row>
-    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="29"/>
       <c r="B74" s="27"/>
       <c r="C74" s="35">
@@ -17115,7 +17121,7 @@
       <c r="J74" s="29"/>
       <c r="K74" s="29"/>
     </row>
-    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="29"/>
       <c r="B75" s="27"/>
       <c r="C75" s="38">
@@ -17136,7 +17142,7 @@
       <c r="J75" s="29"/>
       <c r="K75" s="29"/>
     </row>
-    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="29"/>
       <c r="B76" s="27"/>
       <c r="C76" s="35">
@@ -17157,7 +17163,7 @@
       <c r="J76" s="29"/>
       <c r="K76" s="29"/>
     </row>
-    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="29"/>
       <c r="B77" s="27"/>
       <c r="C77" s="38">
@@ -17178,7 +17184,7 @@
       <c r="J77" s="29"/>
       <c r="K77" s="29"/>
     </row>
-    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="29"/>
       <c r="B78" s="27"/>
       <c r="C78" s="35">
@@ -17199,7 +17205,7 @@
       <c r="J78" s="29"/>
       <c r="K78" s="29"/>
     </row>
-    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="29"/>
       <c r="B79" s="27"/>
       <c r="C79" s="38">
@@ -17220,7 +17226,7 @@
       <c r="J79" s="29"/>
       <c r="K79" s="29"/>
     </row>
-    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="29"/>
       <c r="B80" s="27"/>
       <c r="C80" s="35">
@@ -17241,7 +17247,7 @@
       <c r="J80" s="29"/>
       <c r="K80" s="29"/>
     </row>
-    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="29"/>
       <c r="B81" s="27"/>
       <c r="C81" s="38">
@@ -17262,7 +17268,7 @@
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
     </row>
-    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="29"/>
       <c r="B82" s="27"/>
       <c r="C82" s="35">
@@ -17283,7 +17289,7 @@
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
     </row>
-    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="29"/>
       <c r="B83" s="27"/>
       <c r="C83" s="38">
@@ -17304,7 +17310,7 @@
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
     </row>
-    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="29"/>
       <c r="B84" s="27"/>
       <c r="C84" s="35">
@@ -17325,7 +17331,7 @@
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
     </row>
-    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="29"/>
       <c r="B85" s="27"/>
       <c r="C85" s="38">
@@ -17346,7 +17352,7 @@
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
     </row>
-    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="29"/>
       <c r="B86" s="27"/>
       <c r="C86" s="35">
@@ -17367,7 +17373,7 @@
       <c r="J86" s="29"/>
       <c r="K86" s="29"/>
     </row>
-    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="29"/>
       <c r="B87" s="27"/>
       <c r="C87" s="38">
@@ -17388,7 +17394,7 @@
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
     </row>
-    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="29"/>
       <c r="B88" s="27"/>
       <c r="C88" s="35">
@@ -17409,7 +17415,7 @@
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
     </row>
-    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="29"/>
       <c r="B89" s="27"/>
       <c r="C89" s="38">
@@ -17430,7 +17436,7 @@
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
     </row>
-    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="29"/>
       <c r="B90" s="27"/>
       <c r="C90" s="35">
@@ -17451,7 +17457,7 @@
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
     </row>
-    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="29"/>
       <c r="B91" s="27"/>
       <c r="C91" s="38">
@@ -17472,7 +17478,7 @@
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
     </row>
-    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="29"/>
       <c r="B92" s="27"/>
       <c r="C92" s="35">
@@ -17493,7 +17499,7 @@
       <c r="J92" s="29"/>
       <c r="K92" s="29"/>
     </row>
-    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="29"/>
       <c r="B93" s="27"/>
       <c r="C93" s="38">
@@ -17514,7 +17520,7 @@
       <c r="J93" s="29"/>
       <c r="K93" s="29"/>
     </row>
-    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="29"/>
       <c r="B94" s="27"/>
       <c r="C94" s="35">
@@ -17535,7 +17541,7 @@
       <c r="J94" s="29"/>
       <c r="K94" s="29"/>
     </row>
-    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="29"/>
       <c r="B95" s="27"/>
       <c r="C95" s="38">
@@ -17556,7 +17562,7 @@
       <c r="J95" s="29"/>
       <c r="K95" s="29"/>
     </row>
-    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="29"/>
       <c r="B96" s="27"/>
       <c r="C96" s="35">
@@ -17577,7 +17583,7 @@
       <c r="J96" s="29"/>
       <c r="K96" s="29"/>
     </row>
-    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="29"/>
       <c r="B97" s="27"/>
       <c r="C97" s="38">
@@ -17598,7 +17604,7 @@
       <c r="J97" s="29"/>
       <c r="K97" s="29"/>
     </row>
-    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="29"/>
       <c r="B98" s="27"/>
       <c r="C98" s="35">
@@ -17619,7 +17625,7 @@
       <c r="J98" s="29"/>
       <c r="K98" s="29"/>
     </row>
-    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="29"/>
       <c r="B99" s="27"/>
       <c r="C99" s="38">
@@ -17640,7 +17646,7 @@
       <c r="J99" s="29"/>
       <c r="K99" s="29"/>
     </row>
-    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="29"/>
       <c r="B100" s="27"/>
       <c r="C100" s="35">
@@ -17661,7 +17667,7 @@
       <c r="J100" s="29"/>
       <c r="K100" s="29"/>
     </row>
-    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="29"/>
       <c r="B101" s="27"/>
       <c r="C101" s="38">
@@ -17682,7 +17688,7 @@
       <c r="J101" s="29"/>
       <c r="K101" s="29"/>
     </row>
-    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="29"/>
       <c r="B102" s="27"/>
       <c r="C102" s="35">
@@ -17703,7 +17709,7 @@
       <c r="J102" s="29"/>
       <c r="K102" s="29"/>
     </row>
-    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="29"/>
       <c r="B103" s="27"/>
       <c r="C103" s="38">
@@ -17724,7 +17730,7 @@
       <c r="J103" s="29"/>
       <c r="K103" s="29"/>
     </row>
-    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="29"/>
       <c r="B104" s="27"/>
       <c r="C104" s="35">
@@ -17745,7 +17751,7 @@
       <c r="J104" s="29"/>
       <c r="K104" s="29"/>
     </row>
-    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="29"/>
       <c r="B105" s="27"/>
       <c r="C105" s="38">
@@ -17766,7 +17772,7 @@
       <c r="J105" s="29"/>
       <c r="K105" s="29"/>
     </row>
-    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="29"/>
       <c r="B106" s="27"/>
       <c r="C106" s="35">
@@ -17787,7 +17793,7 @@
       <c r="J106" s="29"/>
       <c r="K106" s="29"/>
     </row>
-    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="29"/>
       <c r="B107" s="27"/>
       <c r="C107" s="38">
@@ -17808,7 +17814,7 @@
       <c r="J107" s="29"/>
       <c r="K107" s="29"/>
     </row>
-    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="29"/>
       <c r="B108" s="27"/>
       <c r="C108" s="35">
@@ -17829,7 +17835,7 @@
       <c r="J108" s="29"/>
       <c r="K108" s="29"/>
     </row>
-    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="29"/>
       <c r="B109" s="27"/>
       <c r="C109" s="38">
@@ -17850,7 +17856,7 @@
       <c r="J109" s="29"/>
       <c r="K109" s="29"/>
     </row>
-    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="29"/>
       <c r="B110" s="27"/>
       <c r="C110" s="35">
@@ -17871,7 +17877,7 @@
       <c r="J110" s="29"/>
       <c r="K110" s="29"/>
     </row>
-    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="29"/>
       <c r="B111" s="27"/>
       <c r="C111" s="38">
@@ -17892,7 +17898,7 @@
       <c r="J111" s="29"/>
       <c r="K111" s="29"/>
     </row>
-    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="29"/>
       <c r="B112" s="27"/>
       <c r="C112" s="35">
@@ -17913,7 +17919,7 @@
       <c r="J112" s="29"/>
       <c r="K112" s="29"/>
     </row>
-    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="29"/>
       <c r="B113" s="27"/>
       <c r="C113" s="38">
@@ -17934,7 +17940,7 @@
       <c r="J113" s="29"/>
       <c r="K113" s="29"/>
     </row>
-    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="29"/>
       <c r="B114" s="27"/>
       <c r="C114" s="35">
@@ -17955,7 +17961,7 @@
       <c r="J114" s="29"/>
       <c r="K114" s="29"/>
     </row>
-    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="29"/>
       <c r="B115" s="27"/>
       <c r="C115" s="38">
@@ -17976,7 +17982,7 @@
       <c r="J115" s="29"/>
       <c r="K115" s="29"/>
     </row>
-    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="29"/>
       <c r="B116" s="27"/>
       <c r="C116" s="35">
@@ -17997,7 +18003,7 @@
       <c r="J116" s="29"/>
       <c r="K116" s="29"/>
     </row>
-    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="29"/>
       <c r="B117" s="27"/>
       <c r="C117" s="38">
@@ -18018,7 +18024,7 @@
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
     </row>
-    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="29"/>
       <c r="B118" s="27"/>
       <c r="C118" s="35">
@@ -18039,7 +18045,7 @@
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
     </row>
-    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="29"/>
       <c r="B119" s="27"/>
       <c r="C119" s="38">
@@ -18060,7 +18066,7 @@
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
     </row>
-    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="29"/>
       <c r="B120" s="27"/>
       <c r="C120" s="35">
@@ -18081,7 +18087,7 @@
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
     </row>
-    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="29"/>
       <c r="B121" s="27"/>
       <c r="C121" s="38">
@@ -18102,7 +18108,7 @@
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
     </row>
-    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="29"/>
       <c r="B122" s="27"/>
       <c r="C122" s="35">
@@ -18123,7 +18129,7 @@
       <c r="J122" s="29"/>
       <c r="K122" s="29"/>
     </row>
-    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="29"/>
       <c r="B123" s="27"/>
       <c r="C123" s="38">
@@ -18144,7 +18150,7 @@
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
     </row>
-    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="29"/>
       <c r="B124" s="27"/>
       <c r="C124" s="35">
@@ -18165,7 +18171,7 @@
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
     </row>
-    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="29"/>
       <c r="B125" s="27"/>
       <c r="C125" s="38">
@@ -18186,7 +18192,7 @@
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
     </row>
-    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="29"/>
       <c r="B126" s="27"/>
       <c r="C126" s="35">
@@ -18207,7 +18213,7 @@
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
     </row>
-    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="29"/>
       <c r="B127" s="27"/>
       <c r="C127" s="38">
@@ -18228,7 +18234,7 @@
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
     </row>
-    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="29"/>
       <c r="B128" s="27"/>
       <c r="C128" s="35">
@@ -18249,7 +18255,7 @@
       <c r="J128" s="29"/>
       <c r="K128" s="29"/>
     </row>
-    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="29"/>
       <c r="B129" s="27"/>
       <c r="C129" s="38">
@@ -18270,7 +18276,7 @@
       <c r="J129" s="29"/>
       <c r="K129" s="29"/>
     </row>
-    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="29"/>
       <c r="B130" s="27"/>
       <c r="C130" s="35">
@@ -18291,7 +18297,7 @@
       <c r="J130" s="29"/>
       <c r="K130" s="29"/>
     </row>
-    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="29"/>
       <c r="B131" s="27"/>
       <c r="C131" s="38">
@@ -18312,7 +18318,7 @@
       <c r="J131" s="29"/>
       <c r="K131" s="29"/>
     </row>
-    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="29"/>
       <c r="B132" s="27"/>
       <c r="C132" s="35">
@@ -18333,7 +18339,7 @@
       <c r="J132" s="29"/>
       <c r="K132" s="29"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="38">
         <v>76</v>
       </c>
@@ -18347,7 +18353,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="35">
         <v>77</v>
       </c>
@@ -18361,7 +18367,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -18375,7 +18381,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C136" s="3">
         <v>79</v>
       </c>
@@ -18412,37 +18418,37 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R136"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="29" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="29" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D2" s="22"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="24" t="s">
         <v>226</v>
       </c>
@@ -18450,7 +18456,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>227</v>
@@ -18458,7 +18464,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>16</v>
@@ -18466,13 +18472,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="26" t="s">
         <v>227</v>
       </c>
@@ -18480,7 +18486,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>7</v>
@@ -18495,7 +18501,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -18509,7 +18515,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -18523,7 +18529,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -18537,7 +18543,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -18551,7 +18557,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -18565,7 +18571,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -18579,7 +18585,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -18593,7 +18599,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -18607,7 +18613,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -18621,7 +18627,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -18635,7 +18641,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -18649,7 +18655,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -18663,7 +18669,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -18677,7 +18683,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -18691,7 +18697,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -18705,7 +18711,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -18719,7 +18725,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -18733,7 +18739,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -18747,7 +18753,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -18761,7 +18767,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -18775,7 +18781,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -18789,7 +18795,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -18803,7 +18809,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -18817,7 +18823,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -18831,7 +18837,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -18845,7 +18851,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -18859,7 +18865,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -18873,7 +18879,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -18887,7 +18893,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -18901,7 +18907,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -18915,7 +18921,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -18929,7 +18935,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -18943,7 +18949,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -18957,7 +18963,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -18971,7 +18977,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -18985,7 +18991,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -18999,7 +19005,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -19013,7 +19019,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -19027,7 +19033,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -19041,7 +19047,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -19055,7 +19061,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -19069,7 +19075,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -19083,7 +19089,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -19097,7 +19103,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -19111,7 +19117,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -19125,7 +19131,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -19139,12 +19145,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="33" t="s">
         <v>7</v>
       </c>
@@ -19158,7 +19164,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="35">
         <v>1</v>
       </c>
@@ -19172,7 +19178,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="38">
         <v>2</v>
       </c>
@@ -19186,7 +19192,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="35">
         <v>3</v>
       </c>
@@ -19200,7 +19206,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="38">
         <v>4</v>
       </c>
@@ -19214,7 +19220,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="35">
         <v>5</v>
       </c>
@@ -19228,7 +19234,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="38">
         <v>6</v>
       </c>
@@ -19242,7 +19248,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="29"/>
       <c r="B64" s="27"/>
       <c r="C64" s="35">
@@ -19263,7 +19269,7 @@
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
     </row>
-    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="29"/>
       <c r="B65" s="27"/>
       <c r="C65" s="38">
@@ -19284,7 +19290,7 @@
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
     </row>
-    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="29"/>
       <c r="B66" s="27"/>
       <c r="C66" s="35">
@@ -19305,7 +19311,7 @@
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
     </row>
-    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="29"/>
       <c r="B67" s="27"/>
       <c r="C67" s="38">
@@ -19326,7 +19332,7 @@
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
     </row>
-    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="29"/>
       <c r="B68" s="27"/>
       <c r="C68" s="35">
@@ -19347,7 +19353,7 @@
       <c r="J68" s="29"/>
       <c r="K68" s="29"/>
     </row>
-    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="29"/>
       <c r="B69" s="27"/>
       <c r="C69" s="38">
@@ -19368,7 +19374,7 @@
       <c r="J69" s="29"/>
       <c r="K69" s="29"/>
     </row>
-    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="29"/>
       <c r="B70" s="27"/>
       <c r="C70" s="35">
@@ -19389,7 +19395,7 @@
       <c r="J70" s="29"/>
       <c r="K70" s="29"/>
     </row>
-    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="29"/>
       <c r="B71" s="27"/>
       <c r="C71" s="38">
@@ -19410,7 +19416,7 @@
       <c r="J71" s="29"/>
       <c r="K71" s="29"/>
     </row>
-    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="29"/>
       <c r="B72" s="27"/>
       <c r="C72" s="35">
@@ -19431,7 +19437,7 @@
       <c r="J72" s="29"/>
       <c r="K72" s="29"/>
     </row>
-    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="29"/>
       <c r="B73" s="27"/>
       <c r="C73" s="38">
@@ -19452,7 +19458,7 @@
       <c r="J73" s="29"/>
       <c r="K73" s="29"/>
     </row>
-    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="29"/>
       <c r="B74" s="27"/>
       <c r="C74" s="35">
@@ -19473,7 +19479,7 @@
       <c r="J74" s="29"/>
       <c r="K74" s="29"/>
     </row>
-    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="29"/>
       <c r="B75" s="27"/>
       <c r="C75" s="38">
@@ -19494,7 +19500,7 @@
       <c r="J75" s="29"/>
       <c r="K75" s="29"/>
     </row>
-    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="29"/>
       <c r="B76" s="27"/>
       <c r="C76" s="35">
@@ -19515,7 +19521,7 @@
       <c r="J76" s="29"/>
       <c r="K76" s="29"/>
     </row>
-    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="29"/>
       <c r="B77" s="27"/>
       <c r="C77" s="38">
@@ -19536,7 +19542,7 @@
       <c r="J77" s="29"/>
       <c r="K77" s="29"/>
     </row>
-    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="29"/>
       <c r="B78" s="27"/>
       <c r="C78" s="35">
@@ -19557,7 +19563,7 @@
       <c r="J78" s="29"/>
       <c r="K78" s="29"/>
     </row>
-    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="29"/>
       <c r="B79" s="27"/>
       <c r="C79" s="38">
@@ -19578,7 +19584,7 @@
       <c r="J79" s="29"/>
       <c r="K79" s="29"/>
     </row>
-    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="29"/>
       <c r="B80" s="27"/>
       <c r="C80" s="35">
@@ -19599,7 +19605,7 @@
       <c r="J80" s="29"/>
       <c r="K80" s="29"/>
     </row>
-    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="29"/>
       <c r="B81" s="27"/>
       <c r="C81" s="38">
@@ -19620,7 +19626,7 @@
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
     </row>
-    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="29"/>
       <c r="B82" s="27"/>
       <c r="C82" s="35">
@@ -19641,7 +19647,7 @@
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
     </row>
-    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="29"/>
       <c r="B83" s="27"/>
       <c r="C83" s="38">
@@ -19662,7 +19668,7 @@
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
     </row>
-    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="29"/>
       <c r="B84" s="27"/>
       <c r="C84" s="35">
@@ -19683,7 +19689,7 @@
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
     </row>
-    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="29"/>
       <c r="B85" s="27"/>
       <c r="C85" s="38">
@@ -19704,7 +19710,7 @@
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
     </row>
-    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="29"/>
       <c r="B86" s="27"/>
       <c r="C86" s="35">
@@ -19725,7 +19731,7 @@
       <c r="J86" s="29"/>
       <c r="K86" s="29"/>
     </row>
-    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="29"/>
       <c r="B87" s="27"/>
       <c r="C87" s="38">
@@ -19746,7 +19752,7 @@
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
     </row>
-    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="29"/>
       <c r="B88" s="27"/>
       <c r="C88" s="35">
@@ -19767,7 +19773,7 @@
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
     </row>
-    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="29"/>
       <c r="B89" s="27"/>
       <c r="C89" s="38">
@@ -19788,7 +19794,7 @@
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
     </row>
-    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="29"/>
       <c r="B90" s="27"/>
       <c r="C90" s="35">
@@ -19809,7 +19815,7 @@
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
     </row>
-    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="29"/>
       <c r="B91" s="27"/>
       <c r="C91" s="38">
@@ -19830,7 +19836,7 @@
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
     </row>
-    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="29"/>
       <c r="B92" s="27"/>
       <c r="C92" s="35">
@@ -19851,7 +19857,7 @@
       <c r="J92" s="29"/>
       <c r="K92" s="29"/>
     </row>
-    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="29"/>
       <c r="B93" s="27"/>
       <c r="C93" s="38">
@@ -19872,7 +19878,7 @@
       <c r="J93" s="29"/>
       <c r="K93" s="29"/>
     </row>
-    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="29"/>
       <c r="B94" s="27"/>
       <c r="C94" s="35">
@@ -19893,7 +19899,7 @@
       <c r="J94" s="29"/>
       <c r="K94" s="29"/>
     </row>
-    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="29"/>
       <c r="B95" s="27"/>
       <c r="C95" s="38">
@@ -19914,7 +19920,7 @@
       <c r="J95" s="29"/>
       <c r="K95" s="29"/>
     </row>
-    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="29"/>
       <c r="B96" s="27"/>
       <c r="C96" s="35">
@@ -19935,7 +19941,7 @@
       <c r="J96" s="29"/>
       <c r="K96" s="29"/>
     </row>
-    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="29"/>
       <c r="B97" s="27"/>
       <c r="C97" s="38">
@@ -19956,7 +19962,7 @@
       <c r="J97" s="29"/>
       <c r="K97" s="29"/>
     </row>
-    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="29"/>
       <c r="B98" s="27"/>
       <c r="C98" s="35">
@@ -19977,7 +19983,7 @@
       <c r="J98" s="29"/>
       <c r="K98" s="29"/>
     </row>
-    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="29"/>
       <c r="B99" s="27"/>
       <c r="C99" s="38">
@@ -19998,7 +20004,7 @@
       <c r="J99" s="29"/>
       <c r="K99" s="29"/>
     </row>
-    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="29"/>
       <c r="B100" s="27"/>
       <c r="C100" s="35">
@@ -20019,7 +20025,7 @@
       <c r="J100" s="29"/>
       <c r="K100" s="29"/>
     </row>
-    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="29"/>
       <c r="B101" s="27"/>
       <c r="C101" s="38">
@@ -20040,7 +20046,7 @@
       <c r="J101" s="29"/>
       <c r="K101" s="29"/>
     </row>
-    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="29"/>
       <c r="B102" s="27"/>
       <c r="C102" s="35">
@@ -20061,7 +20067,7 @@
       <c r="J102" s="29"/>
       <c r="K102" s="29"/>
     </row>
-    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="29"/>
       <c r="B103" s="27"/>
       <c r="C103" s="38">
@@ -20082,7 +20088,7 @@
       <c r="J103" s="29"/>
       <c r="K103" s="29"/>
     </row>
-    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="29"/>
       <c r="B104" s="27"/>
       <c r="C104" s="35">
@@ -20103,7 +20109,7 @@
       <c r="J104" s="29"/>
       <c r="K104" s="29"/>
     </row>
-    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="29"/>
       <c r="B105" s="27"/>
       <c r="C105" s="38">
@@ -20124,7 +20130,7 @@
       <c r="J105" s="29"/>
       <c r="K105" s="29"/>
     </row>
-    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="29"/>
       <c r="B106" s="27"/>
       <c r="C106" s="35">
@@ -20145,7 +20151,7 @@
       <c r="J106" s="29"/>
       <c r="K106" s="29"/>
     </row>
-    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="29"/>
       <c r="B107" s="27"/>
       <c r="C107" s="38">
@@ -20166,7 +20172,7 @@
       <c r="J107" s="29"/>
       <c r="K107" s="29"/>
     </row>
-    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="29"/>
       <c r="B108" s="27"/>
       <c r="C108" s="35">
@@ -20187,7 +20193,7 @@
       <c r="J108" s="29"/>
       <c r="K108" s="29"/>
     </row>
-    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="29"/>
       <c r="B109" s="27"/>
       <c r="C109" s="38">
@@ -20208,7 +20214,7 @@
       <c r="J109" s="29"/>
       <c r="K109" s="29"/>
     </row>
-    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="29"/>
       <c r="B110" s="27"/>
       <c r="C110" s="35">
@@ -20229,7 +20235,7 @@
       <c r="J110" s="29"/>
       <c r="K110" s="29"/>
     </row>
-    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="29"/>
       <c r="B111" s="27"/>
       <c r="C111" s="38">
@@ -20250,7 +20256,7 @@
       <c r="J111" s="29"/>
       <c r="K111" s="29"/>
     </row>
-    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="29"/>
       <c r="B112" s="27"/>
       <c r="C112" s="35">
@@ -20271,7 +20277,7 @@
       <c r="J112" s="29"/>
       <c r="K112" s="29"/>
     </row>
-    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="29"/>
       <c r="B113" s="27"/>
       <c r="C113" s="38">
@@ -20292,7 +20298,7 @@
       <c r="J113" s="29"/>
       <c r="K113" s="29"/>
     </row>
-    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="29"/>
       <c r="B114" s="27"/>
       <c r="C114" s="35">
@@ -20313,7 +20319,7 @@
       <c r="J114" s="29"/>
       <c r="K114" s="29"/>
     </row>
-    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="29"/>
       <c r="B115" s="27"/>
       <c r="C115" s="38">
@@ -20334,7 +20340,7 @@
       <c r="J115" s="29"/>
       <c r="K115" s="29"/>
     </row>
-    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="29"/>
       <c r="B116" s="27"/>
       <c r="C116" s="35">
@@ -20355,7 +20361,7 @@
       <c r="J116" s="29"/>
       <c r="K116" s="29"/>
     </row>
-    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="29"/>
       <c r="B117" s="27"/>
       <c r="C117" s="38">
@@ -20376,7 +20382,7 @@
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
     </row>
-    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="29"/>
       <c r="B118" s="27"/>
       <c r="C118" s="35">
@@ -20397,7 +20403,7 @@
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
     </row>
-    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="29"/>
       <c r="B119" s="27"/>
       <c r="C119" s="38">
@@ -20418,7 +20424,7 @@
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
     </row>
-    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="29"/>
       <c r="B120" s="27"/>
       <c r="C120" s="35">
@@ -20439,7 +20445,7 @@
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
     </row>
-    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="29"/>
       <c r="B121" s="27"/>
       <c r="C121" s="38">
@@ -20460,7 +20466,7 @@
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
     </row>
-    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="29"/>
       <c r="B122" s="27"/>
       <c r="C122" s="35">
@@ -20481,7 +20487,7 @@
       <c r="J122" s="29"/>
       <c r="K122" s="29"/>
     </row>
-    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="29"/>
       <c r="B123" s="27"/>
       <c r="C123" s="38">
@@ -20502,7 +20508,7 @@
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
     </row>
-    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="29"/>
       <c r="B124" s="27"/>
       <c r="C124" s="35">
@@ -20523,7 +20529,7 @@
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
     </row>
-    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="29"/>
       <c r="B125" s="27"/>
       <c r="C125" s="38">
@@ -20544,7 +20550,7 @@
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
     </row>
-    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="29"/>
       <c r="B126" s="27"/>
       <c r="C126" s="35">
@@ -20565,7 +20571,7 @@
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
     </row>
-    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="29"/>
       <c r="B127" s="27"/>
       <c r="C127" s="38">
@@ -20586,7 +20592,7 @@
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
     </row>
-    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="29"/>
       <c r="B128" s="27"/>
       <c r="C128" s="35">
@@ -20607,7 +20613,7 @@
       <c r="J128" s="29"/>
       <c r="K128" s="29"/>
     </row>
-    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="29"/>
       <c r="B129" s="27"/>
       <c r="C129" s="38">
@@ -20628,7 +20634,7 @@
       <c r="J129" s="29"/>
       <c r="K129" s="29"/>
     </row>
-    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="29"/>
       <c r="B130" s="27"/>
       <c r="C130" s="35">
@@ -20649,7 +20655,7 @@
       <c r="J130" s="29"/>
       <c r="K130" s="29"/>
     </row>
-    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="29"/>
       <c r="B131" s="27"/>
       <c r="C131" s="38">
@@ -20670,7 +20676,7 @@
       <c r="J131" s="29"/>
       <c r="K131" s="29"/>
     </row>
-    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="29"/>
       <c r="B132" s="27"/>
       <c r="C132" s="35">
@@ -20691,7 +20697,7 @@
       <c r="J132" s="29"/>
       <c r="K132" s="29"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="38">
         <v>76</v>
       </c>
@@ -20705,7 +20711,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="35">
         <v>77</v>
       </c>
@@ -20719,7 +20725,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -20733,7 +20739,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C136" s="35">
         <v>79</v>
       </c>

--- a/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/ar-sa.xlsx
+++ b/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/ar-sa.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Documents\_Learn\Packaging.tutorial\OS.11\23H2\Expand\Install\Report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5924f5d6bcb7c7fc/Documents/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0931E0C2-5643-4859-B05E-EDA8AB777B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{0931E0C2-5643-4859-B05E-EDA8AB777B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A1AA702-5C56-41ED-94A0-6E33BEEFAAEF}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="5" r:id="rId1"/>
@@ -4741,22 +4741,22 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="84.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="50.3984375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.53125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="120.6640625" style="3" customWidth="1"/>
-    <col min="8" max="10" width="16.6640625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" style="7" customWidth="1"/>
-    <col min="12" max="12" width="2.6640625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.1328125" style="1" hidden="1"/>
+    <col min="1" max="1" width="2.69140625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="84.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50.3828125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.53515625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="120.69140625" style="3" customWidth="1"/>
+    <col min="8" max="10" width="16.69140625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.69140625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="2.69140625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.15234375" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4769,7 +4769,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="80.2" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:12" ht="80.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1"/>
       <c r="C2" s="4" t="s">
         <v>253</v>
@@ -4785,7 +4785,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
       <c r="C3" s="6"/>
       <c r="D3" s="5"/>
@@ -4797,7 +4797,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:12" ht="5.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
@@ -4808,7 +4808,7 @@
       <c r="I4" s="10"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:12" ht="62.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" ht="62.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="11"/>
       <c r="C5" s="11" t="s">
         <v>9</v>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="L5" s="7"/>
     </row>
-    <row r="6" spans="1:12" ht="126" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" ht="126.9" x14ac:dyDescent="0.4">
       <c r="B6" s="13"/>
       <c r="C6" s="14" t="s">
         <v>262</v>
@@ -4868,7 +4868,7 @@
       <c r="K6" s="13"/>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="1:12" ht="94.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" ht="95.15" x14ac:dyDescent="0.4">
       <c r="B7" s="13"/>
       <c r="C7" s="45" t="s">
         <v>263</v>
@@ -4897,17 +4897,13 @@
       <c r="K7" s="46"/>
       <c r="L7" s="7"/>
     </row>
-    <row r="8" spans="1:12" ht="20.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" s="14" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="7"/>
+      <c r="B8" s="3"/>
       <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-    </row>
-    <row r="9" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="9" spans="1:12" s="14" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="7"/>
       <c r="B9" s="16"/>
       <c r="C9" s="17" t="s">
         <v>2</v>
@@ -4916,7 +4912,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:12" s="14" customFormat="1" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="7"/>
       <c r="B10" s="19"/>
       <c r="C10" s="20" t="s">
         <v>0</v>
@@ -4924,14 +4921,9 @@
       <c r="D10" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-    </row>
-    <row r="11" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="11" spans="1:12" s="14" customFormat="1" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="7"/>
       <c r="B11" s="21"/>
       <c r="C11" s="20" t="s">
         <v>1</v>
@@ -4939,31 +4931,21 @@
       <c r="D11" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-    </row>
-    <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:12" s="14" customFormat="1" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="7"/>
+      <c r="B12" s="3"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-    </row>
-    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7"/>
     </row>
-    <row r="14" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -4974,7 +4956,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -4985,7 +4967,7 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -4996,7 +4978,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -5007,7 +4989,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -5018,7 +5000,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -5029,7 +5011,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -5040,7 +5022,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -5051,7 +5033,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -5062,7 +5044,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -5073,7 +5055,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -5084,7 +5066,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -5095,7 +5077,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -5106,7 +5088,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -5117,7 +5099,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -5128,7 +5110,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -5139,7 +5121,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -5150,7 +5132,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -5161,7 +5143,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -5172,7 +5154,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -5183,7 +5165,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" s="7" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -5200,7 +5182,7 @@
   <mergeCells count="1">
     <mergeCell ref="F2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F8:I1048576 F1:I4 H5:J5">
+  <conditionalFormatting sqref="F13:I1048576 F1:I4 H5:J5">
     <cfRule type="iconSet" priority="282">
       <iconSet iconSet="3Symbols2" showValue="0">
         <cfvo type="percent" val="0"/>
@@ -5219,7 +5201,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:I8 H6:J7" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6:J7" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5245,29 +5227,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R135"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="13" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="14" max="15" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="16" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>254</v>
       </c>
@@ -5275,7 +5257,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="24" t="s">
         <v>226</v>
       </c>
@@ -5283,7 +5265,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>227</v>
@@ -5291,7 +5273,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>16</v>
@@ -5299,13 +5281,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="26" t="s">
         <v>227</v>
       </c>
@@ -5313,7 +5295,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>7</v>
@@ -5328,7 +5310,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -5342,7 +5324,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -5356,7 +5338,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -5370,7 +5352,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -5384,7 +5366,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -5398,7 +5380,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -5412,7 +5394,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -5426,7 +5408,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -5440,7 +5422,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -5454,7 +5436,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -5468,7 +5450,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -5482,7 +5464,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -5496,7 +5478,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -5510,7 +5492,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -5524,7 +5506,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -5538,7 +5520,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -5552,7 +5534,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -5566,7 +5548,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -5580,7 +5562,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -5594,7 +5576,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -5608,7 +5590,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -5622,7 +5604,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -5636,7 +5618,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -5650,7 +5632,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -5664,7 +5646,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -5678,7 +5660,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -5692,7 +5674,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -5706,7 +5688,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -5720,7 +5702,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -5734,7 +5716,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -5748,7 +5730,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -5762,7 +5744,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -5776,7 +5758,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -5790,7 +5772,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -5804,7 +5786,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -5818,7 +5800,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -5832,7 +5814,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -5846,7 +5828,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -5860,7 +5842,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -5874,7 +5856,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -5888,7 +5870,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -5902,7 +5884,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -5916,7 +5898,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -5930,7 +5912,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -5944,7 +5926,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -5958,7 +5940,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -5972,7 +5954,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -5986,12 +5968,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="33" t="s">
         <v>7</v>
       </c>
@@ -6005,7 +5987,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="35">
         <v>1</v>
       </c>
@@ -6019,7 +6001,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="38">
         <v>2</v>
       </c>
@@ -6033,7 +6015,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="35">
         <v>3</v>
       </c>
@@ -6047,7 +6029,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="38">
         <v>4</v>
       </c>
@@ -6061,7 +6043,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="35">
         <v>5</v>
       </c>
@@ -6075,7 +6057,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C64" s="38">
         <v>6</v>
       </c>
@@ -6089,7 +6071,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C65" s="35">
         <v>7</v>
       </c>
@@ -6103,7 +6085,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C66" s="38">
         <v>8</v>
       </c>
@@ -6117,7 +6099,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C67" s="35">
         <v>9</v>
       </c>
@@ -6131,7 +6113,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C68" s="38">
         <v>10</v>
       </c>
@@ -6145,7 +6127,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C69" s="35">
         <v>11</v>
       </c>
@@ -6159,7 +6141,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C70" s="38">
         <v>12</v>
       </c>
@@ -6173,7 +6155,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C71" s="35">
         <v>13</v>
       </c>
@@ -6187,7 +6169,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C72" s="38">
         <v>14</v>
       </c>
@@ -6201,7 +6183,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C73" s="35">
         <v>15</v>
       </c>
@@ -6215,7 +6197,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C74" s="38">
         <v>16</v>
       </c>
@@ -6229,7 +6211,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C75" s="35">
         <v>17</v>
       </c>
@@ -6243,7 +6225,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C76" s="38">
         <v>18</v>
       </c>
@@ -6257,7 +6239,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C77" s="35">
         <v>19</v>
       </c>
@@ -6271,7 +6253,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C78" s="38">
         <v>20</v>
       </c>
@@ -6285,7 +6267,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C79" s="35">
         <v>21</v>
       </c>
@@ -6299,7 +6281,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C80" s="38">
         <v>22</v>
       </c>
@@ -6313,7 +6295,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C81" s="35">
         <v>23</v>
       </c>
@@ -6327,7 +6309,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C82" s="38">
         <v>24</v>
       </c>
@@ -6341,7 +6323,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C83" s="35">
         <v>25</v>
       </c>
@@ -6355,7 +6337,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C84" s="38">
         <v>26</v>
       </c>
@@ -6369,7 +6351,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C85" s="35">
         <v>27</v>
       </c>
@@ -6383,7 +6365,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C86" s="38">
         <v>28</v>
       </c>
@@ -6397,7 +6379,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C87" s="35">
         <v>29</v>
       </c>
@@ -6411,7 +6393,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C88" s="38">
         <v>30</v>
       </c>
@@ -6425,7 +6407,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C89" s="35">
         <v>31</v>
       </c>
@@ -6439,7 +6421,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C90" s="38">
         <v>32</v>
       </c>
@@ -6453,7 +6435,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C91" s="35">
         <v>33</v>
       </c>
@@ -6467,7 +6449,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C92" s="38">
         <v>34</v>
       </c>
@@ -6481,7 +6463,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C93" s="35">
         <v>35</v>
       </c>
@@ -6495,7 +6477,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C94" s="38">
         <v>36</v>
       </c>
@@ -6509,7 +6491,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C95" s="35">
         <v>37</v>
       </c>
@@ -6523,7 +6505,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C96" s="38">
         <v>38</v>
       </c>
@@ -6537,7 +6519,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C97" s="35">
         <v>39</v>
       </c>
@@ -6551,7 +6533,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C98" s="38">
         <v>40</v>
       </c>
@@ -6565,7 +6547,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C99" s="35">
         <v>41</v>
       </c>
@@ -6579,7 +6561,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C100" s="38">
         <v>42</v>
       </c>
@@ -6593,7 +6575,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C101" s="35">
         <v>43</v>
       </c>
@@ -6607,7 +6589,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C102" s="38">
         <v>44</v>
       </c>
@@ -6621,7 +6603,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C103" s="35">
         <v>45</v>
       </c>
@@ -6635,7 +6617,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C104" s="38">
         <v>46</v>
       </c>
@@ -6649,7 +6631,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C105" s="35">
         <v>47</v>
       </c>
@@ -6663,7 +6645,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C106" s="38">
         <v>48</v>
       </c>
@@ -6677,7 +6659,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C107" s="35">
         <v>49</v>
       </c>
@@ -6691,7 +6673,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C108" s="38">
         <v>50</v>
       </c>
@@ -6705,7 +6687,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C109" s="35">
         <v>51</v>
       </c>
@@ -6719,7 +6701,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C110" s="38">
         <v>52</v>
       </c>
@@ -6733,7 +6715,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C111" s="35">
         <v>53</v>
       </c>
@@ -6747,7 +6729,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C112" s="38">
         <v>54</v>
       </c>
@@ -6761,7 +6743,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C113" s="35">
         <v>55</v>
       </c>
@@ -6775,7 +6757,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C114" s="38">
         <v>56</v>
       </c>
@@ -6789,7 +6771,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C115" s="35">
         <v>57</v>
       </c>
@@ -6803,7 +6785,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C116" s="38">
         <v>58</v>
       </c>
@@ -6817,7 +6799,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C117" s="35">
         <v>59</v>
       </c>
@@ -6831,7 +6813,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C118" s="38">
         <v>60</v>
       </c>
@@ -6845,7 +6827,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C119" s="35">
         <v>61</v>
       </c>
@@ -6859,7 +6841,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C120" s="38">
         <v>62</v>
       </c>
@@ -6873,7 +6855,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C121" s="35">
         <v>63</v>
       </c>
@@ -6887,7 +6869,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C122" s="38">
         <v>64</v>
       </c>
@@ -6901,7 +6883,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C123" s="35">
         <v>65</v>
       </c>
@@ -6915,7 +6897,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C124" s="38">
         <v>66</v>
       </c>
@@ -6929,7 +6911,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C125" s="35">
         <v>67</v>
       </c>
@@ -6943,7 +6925,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C126" s="38">
         <v>68</v>
       </c>
@@ -6957,7 +6939,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C127" s="35">
         <v>69</v>
       </c>
@@ -6971,7 +6953,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C128" s="38">
         <v>70</v>
       </c>
@@ -6985,7 +6967,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C129" s="35">
         <v>71</v>
       </c>
@@ -6999,7 +6981,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C130" s="38">
         <v>72</v>
       </c>
@@ -7013,7 +6995,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C131" s="35">
         <v>73</v>
       </c>
@@ -7027,7 +7009,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C132" s="38">
         <v>74</v>
       </c>
@@ -7041,7 +7023,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="35">
         <v>75</v>
       </c>
@@ -7055,7 +7037,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="38">
         <v>76</v>
       </c>
@@ -7069,7 +7051,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="3">
         <v>77</v>
       </c>
@@ -7106,29 +7088,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R135"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="13" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="14" max="15" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="14" max="15" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="16" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>255</v>
       </c>
@@ -7136,7 +7118,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="24" t="s">
         <v>226</v>
       </c>
@@ -7144,7 +7126,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>227</v>
@@ -7152,7 +7134,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>16</v>
@@ -7160,13 +7142,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="26" t="s">
         <v>227</v>
       </c>
@@ -7174,7 +7156,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>7</v>
@@ -7189,7 +7171,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -7203,7 +7185,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -7217,7 +7199,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -7231,7 +7213,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -7245,7 +7227,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -7259,7 +7241,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -7273,7 +7255,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -7287,7 +7269,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -7301,7 +7283,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -7315,7 +7297,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -7329,7 +7311,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -7343,7 +7325,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -7357,7 +7339,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -7371,7 +7353,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -7385,7 +7367,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -7399,7 +7381,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -7413,7 +7395,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -7427,7 +7409,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -7441,7 +7423,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -7455,7 +7437,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -7469,7 +7451,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -7483,7 +7465,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -7497,7 +7479,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -7511,7 +7493,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -7525,7 +7507,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -7539,7 +7521,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -7553,7 +7535,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -7567,7 +7549,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -7581,7 +7563,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -7595,7 +7577,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -7609,7 +7591,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -7623,7 +7605,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -7637,7 +7619,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -7651,7 +7633,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -7665,7 +7647,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -7679,7 +7661,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -7693,7 +7675,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -7707,7 +7689,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -7721,7 +7703,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -7735,7 +7717,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -7749,7 +7731,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -7763,7 +7745,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -7777,7 +7759,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -7791,7 +7773,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -7805,7 +7787,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -7819,7 +7801,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -7833,7 +7815,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="55" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -7847,12 +7829,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="33" t="s">
         <v>7</v>
       </c>
@@ -7866,7 +7848,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B59" s="41"/>
       <c r="C59" s="37">
         <v>1</v>
@@ -7881,7 +7863,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B60" s="41"/>
       <c r="C60" s="40">
         <v>2</v>
@@ -7896,7 +7878,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="61" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B61" s="41"/>
       <c r="C61" s="37">
         <v>3</v>
@@ -7911,7 +7893,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B62" s="41"/>
       <c r="C62" s="40">
         <v>4</v>
@@ -7926,7 +7908,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B63" s="41"/>
       <c r="C63" s="37">
         <v>5</v>
@@ -7941,7 +7923,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B64" s="41"/>
       <c r="C64" s="40">
         <v>6</v>
@@ -7956,7 +7938,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="65" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B65" s="41"/>
       <c r="C65" s="37">
         <v>7</v>
@@ -7971,7 +7953,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="66" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B66" s="41"/>
       <c r="C66" s="40">
         <v>8</v>
@@ -7986,7 +7968,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B67" s="41"/>
       <c r="C67" s="37">
         <v>9</v>
@@ -8001,7 +7983,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B68" s="41"/>
       <c r="C68" s="40">
         <v>10</v>
@@ -8016,7 +7998,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="69" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B69" s="41"/>
       <c r="C69" s="37">
         <v>11</v>
@@ -8031,7 +8013,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="70" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B70" s="41"/>
       <c r="C70" s="40">
         <v>12</v>
@@ -8046,7 +8028,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B71" s="41"/>
       <c r="C71" s="37">
         <v>13</v>
@@ -8061,7 +8043,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="72" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B72" s="41"/>
       <c r="C72" s="40">
         <v>14</v>
@@ -8076,7 +8058,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="73" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B73" s="41"/>
       <c r="C73" s="37">
         <v>15</v>
@@ -8091,7 +8073,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="74" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B74" s="41"/>
       <c r="C74" s="40">
         <v>16</v>
@@ -8106,7 +8088,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="75" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B75" s="41"/>
       <c r="C75" s="37">
         <v>17</v>
@@ -8121,7 +8103,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="76" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B76" s="41"/>
       <c r="C76" s="40">
         <v>18</v>
@@ -8136,7 +8118,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="77" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:6" s="42" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B77" s="41"/>
       <c r="C77" s="37">
         <v>19</v>
@@ -8151,7 +8133,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C78" s="38">
         <v>20</v>
       </c>
@@ -8165,7 +8147,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C79" s="35">
         <v>21</v>
       </c>
@@ -8179,7 +8161,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="80" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C80" s="38">
         <v>22</v>
       </c>
@@ -8193,7 +8175,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C81" s="35">
         <v>23</v>
       </c>
@@ -8207,7 +8189,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C82" s="38">
         <v>24</v>
       </c>
@@ -8221,7 +8203,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C83" s="35">
         <v>25</v>
       </c>
@@ -8235,7 +8217,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C84" s="38">
         <v>26</v>
       </c>
@@ -8249,7 +8231,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C85" s="35">
         <v>27</v>
       </c>
@@ -8263,7 +8245,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C86" s="38">
         <v>28</v>
       </c>
@@ -8277,7 +8259,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C87" s="35">
         <v>29</v>
       </c>
@@ -8291,7 +8273,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C88" s="38">
         <v>30</v>
       </c>
@@ -8305,7 +8287,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C89" s="35">
         <v>31</v>
       </c>
@@ -8319,7 +8301,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C90" s="38">
         <v>32</v>
       </c>
@@ -8333,7 +8315,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C91" s="35">
         <v>33</v>
       </c>
@@ -8347,7 +8329,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C92" s="38">
         <v>34</v>
       </c>
@@ -8361,7 +8343,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C93" s="35">
         <v>35</v>
       </c>
@@ -8375,7 +8357,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C94" s="38">
         <v>36</v>
       </c>
@@ -8389,7 +8371,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C95" s="35">
         <v>37</v>
       </c>
@@ -8403,7 +8385,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C96" s="38">
         <v>38</v>
       </c>
@@ -8417,7 +8399,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C97" s="35">
         <v>39</v>
       </c>
@@ -8431,7 +8413,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C98" s="38">
         <v>40</v>
       </c>
@@ -8445,7 +8427,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C99" s="35">
         <v>41</v>
       </c>
@@ -8459,7 +8441,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C100" s="38">
         <v>42</v>
       </c>
@@ -8473,7 +8455,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C101" s="35">
         <v>43</v>
       </c>
@@ -8487,7 +8469,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C102" s="38">
         <v>44</v>
       </c>
@@ -8501,7 +8483,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C103" s="35">
         <v>45</v>
       </c>
@@ -8515,7 +8497,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C104" s="38">
         <v>46</v>
       </c>
@@ -8529,7 +8511,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C105" s="35">
         <v>47</v>
       </c>
@@ -8543,7 +8525,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C106" s="38">
         <v>48</v>
       </c>
@@ -8557,7 +8539,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C107" s="35">
         <v>49</v>
       </c>
@@ -8571,7 +8553,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C108" s="38">
         <v>50</v>
       </c>
@@ -8585,7 +8567,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C109" s="35">
         <v>51</v>
       </c>
@@ -8599,7 +8581,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C110" s="38">
         <v>52</v>
       </c>
@@ -8613,7 +8595,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C111" s="35">
         <v>53</v>
       </c>
@@ -8627,7 +8609,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C112" s="38">
         <v>54</v>
       </c>
@@ -8641,7 +8623,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C113" s="35">
         <v>55</v>
       </c>
@@ -8655,7 +8637,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C114" s="38">
         <v>56</v>
       </c>
@@ -8669,7 +8651,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C115" s="35">
         <v>57</v>
       </c>
@@ -8683,7 +8665,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C116" s="38">
         <v>58</v>
       </c>
@@ -8697,7 +8679,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C117" s="35">
         <v>59</v>
       </c>
@@ -8711,7 +8693,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C118" s="38">
         <v>60</v>
       </c>
@@ -8725,7 +8707,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C119" s="35">
         <v>61</v>
       </c>
@@ -8739,7 +8721,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C120" s="38">
         <v>62</v>
       </c>
@@ -8753,7 +8735,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C121" s="35">
         <v>63</v>
       </c>
@@ -8767,7 +8749,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C122" s="38">
         <v>64</v>
       </c>
@@ -8781,7 +8763,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C123" s="35">
         <v>65</v>
       </c>
@@ -8795,7 +8777,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C124" s="38">
         <v>66</v>
       </c>
@@ -8809,7 +8791,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C125" s="35">
         <v>67</v>
       </c>
@@ -8823,7 +8805,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C126" s="38">
         <v>68</v>
       </c>
@@ -8837,7 +8819,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C127" s="35">
         <v>69</v>
       </c>
@@ -8851,7 +8833,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C128" s="38">
         <v>70</v>
       </c>
@@ -8865,7 +8847,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C129" s="35">
         <v>71</v>
       </c>
@@ -8879,7 +8861,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C130" s="38">
         <v>72</v>
       </c>
@@ -8893,7 +8875,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C131" s="35">
         <v>73</v>
       </c>
@@ -8907,7 +8889,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C132" s="38">
         <v>74</v>
       </c>
@@ -8921,7 +8903,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="35">
         <v>75</v>
       </c>
@@ -8935,7 +8917,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="38">
         <v>76</v>
       </c>
@@ -8949,7 +8931,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="3">
         <v>77</v>
       </c>
@@ -8986,29 +8968,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R136"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>256</v>
       </c>
@@ -9016,7 +8998,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="24" t="s">
         <v>226</v>
       </c>
@@ -9024,7 +9006,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>227</v>
@@ -9032,7 +9014,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>16</v>
@@ -9040,13 +9022,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="26" t="s">
         <v>227</v>
       </c>
@@ -9054,7 +9036,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>7</v>
@@ -9069,7 +9051,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -9083,7 +9065,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -9097,7 +9079,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -9111,7 +9093,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -9125,7 +9107,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -9139,7 +9121,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -9153,7 +9135,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -9167,7 +9149,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -9181,7 +9163,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -9195,7 +9177,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -9209,7 +9191,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -9223,7 +9205,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -9237,7 +9219,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -9251,7 +9233,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -9265,7 +9247,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -9279,7 +9261,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -9293,7 +9275,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -9307,7 +9289,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -9321,7 +9303,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -9335,7 +9317,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -9349,7 +9331,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -9363,7 +9345,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -9377,7 +9359,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -9391,7 +9373,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -9405,7 +9387,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -9419,7 +9401,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -9433,7 +9415,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -9447,7 +9429,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -9461,7 +9443,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -9475,7 +9457,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -9489,7 +9471,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -9503,7 +9485,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -9517,7 +9499,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -9531,7 +9513,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -9545,7 +9527,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -9559,7 +9541,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -9573,7 +9555,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -9587,7 +9569,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -9601,7 +9583,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -9615,7 +9597,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -9629,7 +9611,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -9643,7 +9625,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -9657,7 +9639,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -9671,7 +9653,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -9685,7 +9667,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -9699,7 +9681,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -9713,12 +9695,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="33" t="s">
         <v>7</v>
       </c>
@@ -9732,7 +9714,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="35">
         <v>1</v>
       </c>
@@ -9746,7 +9728,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="38">
         <v>2</v>
       </c>
@@ -9760,7 +9742,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="35">
         <v>3</v>
       </c>
@@ -9774,7 +9756,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="38">
         <v>4</v>
       </c>
@@ -9788,7 +9770,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="35">
         <v>5</v>
       </c>
@@ -9802,7 +9784,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="38">
         <v>6</v>
       </c>
@@ -9816,7 +9798,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="29"/>
       <c r="B64" s="27"/>
       <c r="C64" s="35">
@@ -9837,7 +9819,7 @@
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
     </row>
-    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="29"/>
       <c r="B65" s="27"/>
       <c r="C65" s="38">
@@ -9858,7 +9840,7 @@
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
     </row>
-    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="29"/>
       <c r="B66" s="27"/>
       <c r="C66" s="35">
@@ -9879,7 +9861,7 @@
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
     </row>
-    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="29"/>
       <c r="B67" s="27"/>
       <c r="C67" s="38">
@@ -9900,7 +9882,7 @@
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
     </row>
-    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="29"/>
       <c r="B68" s="27"/>
       <c r="C68" s="35">
@@ -9921,7 +9903,7 @@
       <c r="J68" s="29"/>
       <c r="K68" s="29"/>
     </row>
-    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="29"/>
       <c r="B69" s="27"/>
       <c r="C69" s="38">
@@ -9942,7 +9924,7 @@
       <c r="J69" s="29"/>
       <c r="K69" s="29"/>
     </row>
-    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="29"/>
       <c r="B70" s="27"/>
       <c r="C70" s="35">
@@ -9963,7 +9945,7 @@
       <c r="J70" s="29"/>
       <c r="K70" s="29"/>
     </row>
-    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="29"/>
       <c r="B71" s="27"/>
       <c r="C71" s="38">
@@ -9984,7 +9966,7 @@
       <c r="J71" s="29"/>
       <c r="K71" s="29"/>
     </row>
-    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="29"/>
       <c r="B72" s="27"/>
       <c r="C72" s="35">
@@ -10005,7 +9987,7 @@
       <c r="J72" s="29"/>
       <c r="K72" s="29"/>
     </row>
-    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="29"/>
       <c r="B73" s="27"/>
       <c r="C73" s="38">
@@ -10026,7 +10008,7 @@
       <c r="J73" s="29"/>
       <c r="K73" s="29"/>
     </row>
-    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="29"/>
       <c r="B74" s="27"/>
       <c r="C74" s="35">
@@ -10047,7 +10029,7 @@
       <c r="J74" s="29"/>
       <c r="K74" s="29"/>
     </row>
-    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="29"/>
       <c r="B75" s="27"/>
       <c r="C75" s="38">
@@ -10068,7 +10050,7 @@
       <c r="J75" s="29"/>
       <c r="K75" s="29"/>
     </row>
-    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="29"/>
       <c r="B76" s="27"/>
       <c r="C76" s="35">
@@ -10089,7 +10071,7 @@
       <c r="J76" s="29"/>
       <c r="K76" s="29"/>
     </row>
-    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="29"/>
       <c r="B77" s="27"/>
       <c r="C77" s="38">
@@ -10110,7 +10092,7 @@
       <c r="J77" s="29"/>
       <c r="K77" s="29"/>
     </row>
-    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="29"/>
       <c r="B78" s="27"/>
       <c r="C78" s="35">
@@ -10131,7 +10113,7 @@
       <c r="J78" s="29"/>
       <c r="K78" s="29"/>
     </row>
-    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="29"/>
       <c r="B79" s="27"/>
       <c r="C79" s="38">
@@ -10152,7 +10134,7 @@
       <c r="J79" s="29"/>
       <c r="K79" s="29"/>
     </row>
-    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="29"/>
       <c r="B80" s="27"/>
       <c r="C80" s="35">
@@ -10173,7 +10155,7 @@
       <c r="J80" s="29"/>
       <c r="K80" s="29"/>
     </row>
-    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="29"/>
       <c r="B81" s="27"/>
       <c r="C81" s="38">
@@ -10194,7 +10176,7 @@
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
     </row>
-    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="29"/>
       <c r="B82" s="27"/>
       <c r="C82" s="35">
@@ -10215,7 +10197,7 @@
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
     </row>
-    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="29"/>
       <c r="B83" s="27"/>
       <c r="C83" s="38">
@@ -10236,7 +10218,7 @@
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
     </row>
-    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="29"/>
       <c r="B84" s="27"/>
       <c r="C84" s="35">
@@ -10257,7 +10239,7 @@
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
     </row>
-    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="29"/>
       <c r="B85" s="27"/>
       <c r="C85" s="38">
@@ -10278,7 +10260,7 @@
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
     </row>
-    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="29"/>
       <c r="B86" s="27"/>
       <c r="C86" s="35">
@@ -10299,7 +10281,7 @@
       <c r="J86" s="29"/>
       <c r="K86" s="29"/>
     </row>
-    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="29"/>
       <c r="B87" s="27"/>
       <c r="C87" s="38">
@@ -10320,7 +10302,7 @@
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
     </row>
-    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="29"/>
       <c r="B88" s="27"/>
       <c r="C88" s="35">
@@ -10341,7 +10323,7 @@
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
     </row>
-    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="29"/>
       <c r="B89" s="27"/>
       <c r="C89" s="38">
@@ -10362,7 +10344,7 @@
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
     </row>
-    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="29"/>
       <c r="B90" s="27"/>
       <c r="C90" s="35">
@@ -10383,7 +10365,7 @@
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
     </row>
-    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="29"/>
       <c r="B91" s="27"/>
       <c r="C91" s="38">
@@ -10404,7 +10386,7 @@
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
     </row>
-    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="29"/>
       <c r="B92" s="27"/>
       <c r="C92" s="35">
@@ -10425,7 +10407,7 @@
       <c r="J92" s="29"/>
       <c r="K92" s="29"/>
     </row>
-    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="29"/>
       <c r="B93" s="27"/>
       <c r="C93" s="38">
@@ -10446,7 +10428,7 @@
       <c r="J93" s="29"/>
       <c r="K93" s="29"/>
     </row>
-    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="29"/>
       <c r="B94" s="27"/>
       <c r="C94" s="35">
@@ -10467,7 +10449,7 @@
       <c r="J94" s="29"/>
       <c r="K94" s="29"/>
     </row>
-    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="29"/>
       <c r="B95" s="27"/>
       <c r="C95" s="38">
@@ -10488,7 +10470,7 @@
       <c r="J95" s="29"/>
       <c r="K95" s="29"/>
     </row>
-    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="29"/>
       <c r="B96" s="27"/>
       <c r="C96" s="35">
@@ -10509,7 +10491,7 @@
       <c r="J96" s="29"/>
       <c r="K96" s="29"/>
     </row>
-    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="29"/>
       <c r="B97" s="27"/>
       <c r="C97" s="38">
@@ -10530,7 +10512,7 @@
       <c r="J97" s="29"/>
       <c r="K97" s="29"/>
     </row>
-    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="29"/>
       <c r="B98" s="27"/>
       <c r="C98" s="35">
@@ -10551,7 +10533,7 @@
       <c r="J98" s="29"/>
       <c r="K98" s="29"/>
     </row>
-    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="29"/>
       <c r="B99" s="27"/>
       <c r="C99" s="38">
@@ -10572,7 +10554,7 @@
       <c r="J99" s="29"/>
       <c r="K99" s="29"/>
     </row>
-    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="29"/>
       <c r="B100" s="27"/>
       <c r="C100" s="35">
@@ -10593,7 +10575,7 @@
       <c r="J100" s="29"/>
       <c r="K100" s="29"/>
     </row>
-    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="29"/>
       <c r="B101" s="27"/>
       <c r="C101" s="38">
@@ -10614,7 +10596,7 @@
       <c r="J101" s="29"/>
       <c r="K101" s="29"/>
     </row>
-    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="29"/>
       <c r="B102" s="27"/>
       <c r="C102" s="35">
@@ -10635,7 +10617,7 @@
       <c r="J102" s="29"/>
       <c r="K102" s="29"/>
     </row>
-    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="29"/>
       <c r="B103" s="27"/>
       <c r="C103" s="38">
@@ -10656,7 +10638,7 @@
       <c r="J103" s="29"/>
       <c r="K103" s="29"/>
     </row>
-    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="29"/>
       <c r="B104" s="27"/>
       <c r="C104" s="35">
@@ -10677,7 +10659,7 @@
       <c r="J104" s="29"/>
       <c r="K104" s="29"/>
     </row>
-    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="29"/>
       <c r="B105" s="27"/>
       <c r="C105" s="38">
@@ -10698,7 +10680,7 @@
       <c r="J105" s="29"/>
       <c r="K105" s="29"/>
     </row>
-    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="29"/>
       <c r="B106" s="27"/>
       <c r="C106" s="35">
@@ -10719,7 +10701,7 @@
       <c r="J106" s="29"/>
       <c r="K106" s="29"/>
     </row>
-    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="29"/>
       <c r="B107" s="27"/>
       <c r="C107" s="38">
@@ -10740,7 +10722,7 @@
       <c r="J107" s="29"/>
       <c r="K107" s="29"/>
     </row>
-    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="29"/>
       <c r="B108" s="27"/>
       <c r="C108" s="35">
@@ -10761,7 +10743,7 @@
       <c r="J108" s="29"/>
       <c r="K108" s="29"/>
     </row>
-    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="29"/>
       <c r="B109" s="27"/>
       <c r="C109" s="38">
@@ -10782,7 +10764,7 @@
       <c r="J109" s="29"/>
       <c r="K109" s="29"/>
     </row>
-    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="29"/>
       <c r="B110" s="27"/>
       <c r="C110" s="35">
@@ -10803,7 +10785,7 @@
       <c r="J110" s="29"/>
       <c r="K110" s="29"/>
     </row>
-    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="29"/>
       <c r="B111" s="27"/>
       <c r="C111" s="38">
@@ -10824,7 +10806,7 @@
       <c r="J111" s="29"/>
       <c r="K111" s="29"/>
     </row>
-    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="29"/>
       <c r="B112" s="27"/>
       <c r="C112" s="35">
@@ -10845,7 +10827,7 @@
       <c r="J112" s="29"/>
       <c r="K112" s="29"/>
     </row>
-    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="29"/>
       <c r="B113" s="27"/>
       <c r="C113" s="38">
@@ -10866,7 +10848,7 @@
       <c r="J113" s="29"/>
       <c r="K113" s="29"/>
     </row>
-    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="29"/>
       <c r="B114" s="27"/>
       <c r="C114" s="35">
@@ -10887,7 +10869,7 @@
       <c r="J114" s="29"/>
       <c r="K114" s="29"/>
     </row>
-    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="29"/>
       <c r="B115" s="27"/>
       <c r="C115" s="38">
@@ -10908,7 +10890,7 @@
       <c r="J115" s="29"/>
       <c r="K115" s="29"/>
     </row>
-    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="29"/>
       <c r="B116" s="27"/>
       <c r="C116" s="35">
@@ -10929,7 +10911,7 @@
       <c r="J116" s="29"/>
       <c r="K116" s="29"/>
     </row>
-    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="29"/>
       <c r="B117" s="27"/>
       <c r="C117" s="38">
@@ -10950,7 +10932,7 @@
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
     </row>
-    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="29"/>
       <c r="B118" s="27"/>
       <c r="C118" s="35">
@@ -10971,7 +10953,7 @@
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
     </row>
-    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="29"/>
       <c r="B119" s="27"/>
       <c r="C119" s="38">
@@ -10992,7 +10974,7 @@
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
     </row>
-    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="29"/>
       <c r="B120" s="27"/>
       <c r="C120" s="35">
@@ -11013,7 +10995,7 @@
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
     </row>
-    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="29"/>
       <c r="B121" s="27"/>
       <c r="C121" s="38">
@@ -11034,7 +11016,7 @@
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
     </row>
-    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="29"/>
       <c r="B122" s="27"/>
       <c r="C122" s="35">
@@ -11055,7 +11037,7 @@
       <c r="J122" s="29"/>
       <c r="K122" s="29"/>
     </row>
-    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="29"/>
       <c r="B123" s="27"/>
       <c r="C123" s="38">
@@ -11076,7 +11058,7 @@
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
     </row>
-    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="29"/>
       <c r="B124" s="27"/>
       <c r="C124" s="35">
@@ -11097,7 +11079,7 @@
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
     </row>
-    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="29"/>
       <c r="B125" s="27"/>
       <c r="C125" s="38">
@@ -11118,7 +11100,7 @@
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
     </row>
-    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="29"/>
       <c r="B126" s="27"/>
       <c r="C126" s="35">
@@ -11139,7 +11121,7 @@
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
     </row>
-    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="29"/>
       <c r="B127" s="27"/>
       <c r="C127" s="38">
@@ -11160,7 +11142,7 @@
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
     </row>
-    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="29"/>
       <c r="B128" s="27"/>
       <c r="C128" s="35">
@@ -11181,7 +11163,7 @@
       <c r="J128" s="29"/>
       <c r="K128" s="29"/>
     </row>
-    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="29"/>
       <c r="B129" s="27"/>
       <c r="C129" s="38">
@@ -11202,7 +11184,7 @@
       <c r="J129" s="29"/>
       <c r="K129" s="29"/>
     </row>
-    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="29"/>
       <c r="B130" s="27"/>
       <c r="C130" s="35">
@@ -11223,7 +11205,7 @@
       <c r="J130" s="29"/>
       <c r="K130" s="29"/>
     </row>
-    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="29"/>
       <c r="B131" s="27"/>
       <c r="C131" s="38">
@@ -11244,7 +11226,7 @@
       <c r="J131" s="29"/>
       <c r="K131" s="29"/>
     </row>
-    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="29"/>
       <c r="B132" s="27"/>
       <c r="C132" s="35">
@@ -11265,7 +11247,7 @@
       <c r="J132" s="29"/>
       <c r="K132" s="29"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="38">
         <v>76</v>
       </c>
@@ -11279,7 +11261,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="35">
         <v>77</v>
       </c>
@@ -11293,7 +11275,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="38">
         <v>78</v>
       </c>
@@ -11307,7 +11289,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="3">
         <v>79</v>
       </c>
@@ -11344,29 +11326,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R136"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>257</v>
       </c>
@@ -11374,7 +11356,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="24" t="s">
         <v>226</v>
       </c>
@@ -11382,7 +11364,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>227</v>
@@ -11390,7 +11372,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>16</v>
@@ -11398,13 +11380,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="26" t="s">
         <v>227</v>
       </c>
@@ -11412,7 +11394,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>7</v>
@@ -11427,7 +11409,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -11441,7 +11423,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -11455,7 +11437,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -11469,7 +11451,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -11483,7 +11465,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -11497,7 +11479,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -11511,7 +11493,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -11525,7 +11507,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -11539,7 +11521,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -11553,7 +11535,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -11567,7 +11549,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -11581,7 +11563,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -11595,7 +11577,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -11609,7 +11591,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -11623,7 +11605,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -11637,7 +11619,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -11651,7 +11633,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -11665,7 +11647,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -11679,7 +11661,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -11693,7 +11675,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -11707,7 +11689,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -11721,7 +11703,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -11735,7 +11717,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -11749,7 +11731,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -11763,7 +11745,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -11777,7 +11759,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -11791,7 +11773,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -11805,7 +11787,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -11819,7 +11801,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -11833,7 +11815,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -11847,7 +11829,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -11861,7 +11843,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -11875,7 +11857,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -11889,7 +11871,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -11903,7 +11885,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -11917,7 +11899,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -11931,7 +11913,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -11945,7 +11927,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -11959,7 +11941,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -11973,7 +11955,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -11987,7 +11969,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -12001,7 +11983,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -12015,7 +11997,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -12029,7 +12011,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -12043,7 +12025,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -12057,7 +12039,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -12071,12 +12053,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="33" t="s">
         <v>7</v>
       </c>
@@ -12090,7 +12072,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="35">
         <v>1</v>
       </c>
@@ -12104,7 +12086,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="38">
         <v>2</v>
       </c>
@@ -12118,7 +12100,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="35">
         <v>3</v>
       </c>
@@ -12132,7 +12114,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="38">
         <v>4</v>
       </c>
@@ -12146,7 +12128,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="35">
         <v>5</v>
       </c>
@@ -12160,7 +12142,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="38">
         <v>6</v>
       </c>
@@ -12174,7 +12156,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="29"/>
       <c r="B64" s="27"/>
       <c r="C64" s="35">
@@ -12195,7 +12177,7 @@
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
     </row>
-    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="29"/>
       <c r="B65" s="27"/>
       <c r="C65" s="38">
@@ -12216,7 +12198,7 @@
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
     </row>
-    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="29"/>
       <c r="B66" s="27"/>
       <c r="C66" s="35">
@@ -12237,7 +12219,7 @@
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
     </row>
-    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="29"/>
       <c r="B67" s="27"/>
       <c r="C67" s="38">
@@ -12258,7 +12240,7 @@
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
     </row>
-    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="29"/>
       <c r="B68" s="27"/>
       <c r="C68" s="35">
@@ -12279,7 +12261,7 @@
       <c r="J68" s="29"/>
       <c r="K68" s="29"/>
     </row>
-    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="29"/>
       <c r="B69" s="27"/>
       <c r="C69" s="38">
@@ -12300,7 +12282,7 @@
       <c r="J69" s="29"/>
       <c r="K69" s="29"/>
     </row>
-    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="29"/>
       <c r="B70" s="27"/>
       <c r="C70" s="35">
@@ -12321,7 +12303,7 @@
       <c r="J70" s="29"/>
       <c r="K70" s="29"/>
     </row>
-    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="29"/>
       <c r="B71" s="27"/>
       <c r="C71" s="38">
@@ -12342,7 +12324,7 @@
       <c r="J71" s="29"/>
       <c r="K71" s="29"/>
     </row>
-    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="29"/>
       <c r="B72" s="27"/>
       <c r="C72" s="35">
@@ -12363,7 +12345,7 @@
       <c r="J72" s="29"/>
       <c r="K72" s="29"/>
     </row>
-    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="29"/>
       <c r="B73" s="27"/>
       <c r="C73" s="38">
@@ -12384,7 +12366,7 @@
       <c r="J73" s="29"/>
       <c r="K73" s="29"/>
     </row>
-    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="29"/>
       <c r="B74" s="27"/>
       <c r="C74" s="35">
@@ -12405,7 +12387,7 @@
       <c r="J74" s="29"/>
       <c r="K74" s="29"/>
     </row>
-    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="29"/>
       <c r="B75" s="27"/>
       <c r="C75" s="38">
@@ -12426,7 +12408,7 @@
       <c r="J75" s="29"/>
       <c r="K75" s="29"/>
     </row>
-    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="29"/>
       <c r="B76" s="27"/>
       <c r="C76" s="35">
@@ -12447,7 +12429,7 @@
       <c r="J76" s="29"/>
       <c r="K76" s="29"/>
     </row>
-    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="29"/>
       <c r="B77" s="27"/>
       <c r="C77" s="38">
@@ -12468,7 +12450,7 @@
       <c r="J77" s="29"/>
       <c r="K77" s="29"/>
     </row>
-    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="29"/>
       <c r="B78" s="27"/>
       <c r="C78" s="35">
@@ -12489,7 +12471,7 @@
       <c r="J78" s="29"/>
       <c r="K78" s="29"/>
     </row>
-    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="29"/>
       <c r="B79" s="27"/>
       <c r="C79" s="38">
@@ -12510,7 +12492,7 @@
       <c r="J79" s="29"/>
       <c r="K79" s="29"/>
     </row>
-    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="29"/>
       <c r="B80" s="27"/>
       <c r="C80" s="35">
@@ -12531,7 +12513,7 @@
       <c r="J80" s="29"/>
       <c r="K80" s="29"/>
     </row>
-    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="29"/>
       <c r="B81" s="27"/>
       <c r="C81" s="38">
@@ -12552,7 +12534,7 @@
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
     </row>
-    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="29"/>
       <c r="B82" s="27"/>
       <c r="C82" s="35">
@@ -12573,7 +12555,7 @@
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
     </row>
-    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="29"/>
       <c r="B83" s="27"/>
       <c r="C83" s="38">
@@ -12594,7 +12576,7 @@
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
     </row>
-    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="29"/>
       <c r="B84" s="27"/>
       <c r="C84" s="35">
@@ -12615,7 +12597,7 @@
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
     </row>
-    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="29"/>
       <c r="B85" s="27"/>
       <c r="C85" s="38">
@@ -12636,7 +12618,7 @@
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
     </row>
-    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="29"/>
       <c r="B86" s="27"/>
       <c r="C86" s="35">
@@ -12657,7 +12639,7 @@
       <c r="J86" s="29"/>
       <c r="K86" s="29"/>
     </row>
-    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="29"/>
       <c r="B87" s="27"/>
       <c r="C87" s="38">
@@ -12678,7 +12660,7 @@
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
     </row>
-    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="29"/>
       <c r="B88" s="27"/>
       <c r="C88" s="35">
@@ -12699,7 +12681,7 @@
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
     </row>
-    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="29"/>
       <c r="B89" s="27"/>
       <c r="C89" s="38">
@@ -12720,7 +12702,7 @@
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
     </row>
-    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="29"/>
       <c r="B90" s="27"/>
       <c r="C90" s="35">
@@ -12741,7 +12723,7 @@
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
     </row>
-    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="29"/>
       <c r="B91" s="27"/>
       <c r="C91" s="38">
@@ -12762,7 +12744,7 @@
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
     </row>
-    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="29"/>
       <c r="B92" s="27"/>
       <c r="C92" s="35">
@@ -12783,7 +12765,7 @@
       <c r="J92" s="29"/>
       <c r="K92" s="29"/>
     </row>
-    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="29"/>
       <c r="B93" s="27"/>
       <c r="C93" s="38">
@@ -12804,7 +12786,7 @@
       <c r="J93" s="29"/>
       <c r="K93" s="29"/>
     </row>
-    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="29"/>
       <c r="B94" s="27"/>
       <c r="C94" s="35">
@@ -12825,7 +12807,7 @@
       <c r="J94" s="29"/>
       <c r="K94" s="29"/>
     </row>
-    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="29"/>
       <c r="B95" s="27"/>
       <c r="C95" s="38">
@@ -12846,7 +12828,7 @@
       <c r="J95" s="29"/>
       <c r="K95" s="29"/>
     </row>
-    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="29"/>
       <c r="B96" s="27"/>
       <c r="C96" s="35">
@@ -12867,7 +12849,7 @@
       <c r="J96" s="29"/>
       <c r="K96" s="29"/>
     </row>
-    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="29"/>
       <c r="B97" s="27"/>
       <c r="C97" s="38">
@@ -12888,7 +12870,7 @@
       <c r="J97" s="29"/>
       <c r="K97" s="29"/>
     </row>
-    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="29"/>
       <c r="B98" s="27"/>
       <c r="C98" s="35">
@@ -12909,7 +12891,7 @@
       <c r="J98" s="29"/>
       <c r="K98" s="29"/>
     </row>
-    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="29"/>
       <c r="B99" s="27"/>
       <c r="C99" s="38">
@@ -12930,7 +12912,7 @@
       <c r="J99" s="29"/>
       <c r="K99" s="29"/>
     </row>
-    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="29"/>
       <c r="B100" s="27"/>
       <c r="C100" s="35">
@@ -12951,7 +12933,7 @@
       <c r="J100" s="29"/>
       <c r="K100" s="29"/>
     </row>
-    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="29"/>
       <c r="B101" s="27"/>
       <c r="C101" s="38">
@@ -12972,7 +12954,7 @@
       <c r="J101" s="29"/>
       <c r="K101" s="29"/>
     </row>
-    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="29"/>
       <c r="B102" s="27"/>
       <c r="C102" s="35">
@@ -12993,7 +12975,7 @@
       <c r="J102" s="29"/>
       <c r="K102" s="29"/>
     </row>
-    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="29"/>
       <c r="B103" s="27"/>
       <c r="C103" s="38">
@@ -13014,7 +12996,7 @@
       <c r="J103" s="29"/>
       <c r="K103" s="29"/>
     </row>
-    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="29"/>
       <c r="B104" s="27"/>
       <c r="C104" s="35">
@@ -13035,7 +13017,7 @@
       <c r="J104" s="29"/>
       <c r="K104" s="29"/>
     </row>
-    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="29"/>
       <c r="B105" s="27"/>
       <c r="C105" s="38">
@@ -13056,7 +13038,7 @@
       <c r="J105" s="29"/>
       <c r="K105" s="29"/>
     </row>
-    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="29"/>
       <c r="B106" s="27"/>
       <c r="C106" s="35">
@@ -13077,7 +13059,7 @@
       <c r="J106" s="29"/>
       <c r="K106" s="29"/>
     </row>
-    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="29"/>
       <c r="B107" s="27"/>
       <c r="C107" s="38">
@@ -13098,7 +13080,7 @@
       <c r="J107" s="29"/>
       <c r="K107" s="29"/>
     </row>
-    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="29"/>
       <c r="B108" s="27"/>
       <c r="C108" s="35">
@@ -13119,7 +13101,7 @@
       <c r="J108" s="29"/>
       <c r="K108" s="29"/>
     </row>
-    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="29"/>
       <c r="B109" s="27"/>
       <c r="C109" s="38">
@@ -13140,7 +13122,7 @@
       <c r="J109" s="29"/>
       <c r="K109" s="29"/>
     </row>
-    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="29"/>
       <c r="B110" s="27"/>
       <c r="C110" s="35">
@@ -13161,7 +13143,7 @@
       <c r="J110" s="29"/>
       <c r="K110" s="29"/>
     </row>
-    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="29"/>
       <c r="B111" s="27"/>
       <c r="C111" s="38">
@@ -13182,7 +13164,7 @@
       <c r="J111" s="29"/>
       <c r="K111" s="29"/>
     </row>
-    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="29"/>
       <c r="B112" s="27"/>
       <c r="C112" s="35">
@@ -13203,7 +13185,7 @@
       <c r="J112" s="29"/>
       <c r="K112" s="29"/>
     </row>
-    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="29"/>
       <c r="B113" s="27"/>
       <c r="C113" s="38">
@@ -13224,7 +13206,7 @@
       <c r="J113" s="29"/>
       <c r="K113" s="29"/>
     </row>
-    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="29"/>
       <c r="B114" s="27"/>
       <c r="C114" s="35">
@@ -13245,7 +13227,7 @@
       <c r="J114" s="29"/>
       <c r="K114" s="29"/>
     </row>
-    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="29"/>
       <c r="B115" s="27"/>
       <c r="C115" s="38">
@@ -13266,7 +13248,7 @@
       <c r="J115" s="29"/>
       <c r="K115" s="29"/>
     </row>
-    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="29"/>
       <c r="B116" s="27"/>
       <c r="C116" s="35">
@@ -13287,7 +13269,7 @@
       <c r="J116" s="29"/>
       <c r="K116" s="29"/>
     </row>
-    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="29"/>
       <c r="B117" s="27"/>
       <c r="C117" s="38">
@@ -13308,7 +13290,7 @@
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
     </row>
-    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="29"/>
       <c r="B118" s="27"/>
       <c r="C118" s="35">
@@ -13329,7 +13311,7 @@
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
     </row>
-    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="29"/>
       <c r="B119" s="27"/>
       <c r="C119" s="38">
@@ -13350,7 +13332,7 @@
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
     </row>
-    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="29"/>
       <c r="B120" s="27"/>
       <c r="C120" s="35">
@@ -13371,7 +13353,7 @@
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
     </row>
-    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="29"/>
       <c r="B121" s="27"/>
       <c r="C121" s="38">
@@ -13392,7 +13374,7 @@
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
     </row>
-    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="29"/>
       <c r="B122" s="27"/>
       <c r="C122" s="35">
@@ -13413,7 +13395,7 @@
       <c r="J122" s="29"/>
       <c r="K122" s="29"/>
     </row>
-    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="29"/>
       <c r="B123" s="27"/>
       <c r="C123" s="38">
@@ -13434,7 +13416,7 @@
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
     </row>
-    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="29"/>
       <c r="B124" s="27"/>
       <c r="C124" s="35">
@@ -13455,7 +13437,7 @@
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
     </row>
-    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="29"/>
       <c r="B125" s="27"/>
       <c r="C125" s="38">
@@ -13476,7 +13458,7 @@
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
     </row>
-    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="29"/>
       <c r="B126" s="27"/>
       <c r="C126" s="35">
@@ -13497,7 +13479,7 @@
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
     </row>
-    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="29"/>
       <c r="B127" s="27"/>
       <c r="C127" s="38">
@@ -13518,7 +13500,7 @@
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
     </row>
-    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="29"/>
       <c r="B128" s="27"/>
       <c r="C128" s="35">
@@ -13539,7 +13521,7 @@
       <c r="J128" s="29"/>
       <c r="K128" s="29"/>
     </row>
-    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="29"/>
       <c r="B129" s="27"/>
       <c r="C129" s="38">
@@ -13560,7 +13542,7 @@
       <c r="J129" s="29"/>
       <c r="K129" s="29"/>
     </row>
-    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="29"/>
       <c r="B130" s="27"/>
       <c r="C130" s="35">
@@ -13581,7 +13563,7 @@
       <c r="J130" s="29"/>
       <c r="K130" s="29"/>
     </row>
-    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="29"/>
       <c r="B131" s="27"/>
       <c r="C131" s="38">
@@ -13602,7 +13584,7 @@
       <c r="J131" s="29"/>
       <c r="K131" s="29"/>
     </row>
-    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="29"/>
       <c r="B132" s="27"/>
       <c r="C132" s="35">
@@ -13623,7 +13605,7 @@
       <c r="J132" s="29"/>
       <c r="K132" s="29"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="38">
         <v>76</v>
       </c>
@@ -13637,7 +13619,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="35">
         <v>77</v>
       </c>
@@ -13651,7 +13633,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="38">
         <v>78</v>
       </c>
@@ -13665,7 +13647,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="3">
         <v>79</v>
       </c>
@@ -13702,29 +13684,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R136"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>258</v>
       </c>
@@ -13732,7 +13714,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="24" t="s">
         <v>226</v>
       </c>
@@ -13740,7 +13722,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>227</v>
@@ -13748,7 +13730,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>16</v>
@@ -13756,13 +13738,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="26" t="s">
         <v>227</v>
       </c>
@@ -13770,7 +13752,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>7</v>
@@ -13785,7 +13767,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -13799,7 +13781,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -13813,7 +13795,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -13827,7 +13809,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -13841,7 +13823,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -13855,7 +13837,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -13869,7 +13851,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -13883,7 +13865,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -13897,7 +13879,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -13911,7 +13893,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -13925,7 +13907,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -13939,7 +13921,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -13953,7 +13935,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -13967,7 +13949,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -13981,7 +13963,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -13995,7 +13977,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -14009,7 +13991,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -14023,7 +14005,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -14037,7 +14019,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -14051,7 +14033,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -14065,7 +14047,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -14079,7 +14061,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -14093,7 +14075,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -14107,7 +14089,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -14121,7 +14103,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -14135,7 +14117,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -14149,7 +14131,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -14163,7 +14145,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -14177,7 +14159,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -14191,7 +14173,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -14205,7 +14187,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -14219,7 +14201,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -14233,7 +14215,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -14247,7 +14229,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -14261,7 +14243,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -14275,7 +14257,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -14289,7 +14271,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -14303,7 +14285,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -14317,7 +14299,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -14331,7 +14313,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -14345,7 +14327,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -14359,7 +14341,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -14373,7 +14355,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -14387,7 +14369,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -14401,7 +14383,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -14415,7 +14397,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -14429,12 +14411,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="33" t="s">
         <v>7</v>
       </c>
@@ -14448,7 +14430,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="35">
         <v>1</v>
       </c>
@@ -14462,7 +14444,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="38">
         <v>2</v>
       </c>
@@ -14476,7 +14458,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="35">
         <v>3</v>
       </c>
@@ -14490,7 +14472,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="38">
         <v>4</v>
       </c>
@@ -14504,7 +14486,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="35">
         <v>5</v>
       </c>
@@ -14518,7 +14500,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="38">
         <v>6</v>
       </c>
@@ -14532,7 +14514,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="29"/>
       <c r="B64" s="27"/>
       <c r="C64" s="35">
@@ -14553,7 +14535,7 @@
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
     </row>
-    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="29"/>
       <c r="B65" s="27"/>
       <c r="C65" s="38">
@@ -14574,7 +14556,7 @@
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
     </row>
-    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="29"/>
       <c r="B66" s="27"/>
       <c r="C66" s="35">
@@ -14595,7 +14577,7 @@
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
     </row>
-    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="29"/>
       <c r="B67" s="27"/>
       <c r="C67" s="38">
@@ -14616,7 +14598,7 @@
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
     </row>
-    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="29"/>
       <c r="B68" s="27"/>
       <c r="C68" s="35">
@@ -14637,7 +14619,7 @@
       <c r="J68" s="29"/>
       <c r="K68" s="29"/>
     </row>
-    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="29"/>
       <c r="B69" s="27"/>
       <c r="C69" s="38">
@@ -14658,7 +14640,7 @@
       <c r="J69" s="29"/>
       <c r="K69" s="29"/>
     </row>
-    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="29"/>
       <c r="B70" s="27"/>
       <c r="C70" s="35">
@@ -14679,7 +14661,7 @@
       <c r="J70" s="29"/>
       <c r="K70" s="29"/>
     </row>
-    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="29"/>
       <c r="B71" s="27"/>
       <c r="C71" s="38">
@@ -14700,7 +14682,7 @@
       <c r="J71" s="29"/>
       <c r="K71" s="29"/>
     </row>
-    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="29"/>
       <c r="B72" s="27"/>
       <c r="C72" s="35">
@@ -14721,7 +14703,7 @@
       <c r="J72" s="29"/>
       <c r="K72" s="29"/>
     </row>
-    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="29"/>
       <c r="B73" s="27"/>
       <c r="C73" s="38">
@@ -14742,7 +14724,7 @@
       <c r="J73" s="29"/>
       <c r="K73" s="29"/>
     </row>
-    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="29"/>
       <c r="B74" s="27"/>
       <c r="C74" s="35">
@@ -14763,7 +14745,7 @@
       <c r="J74" s="29"/>
       <c r="K74" s="29"/>
     </row>
-    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="29"/>
       <c r="B75" s="27"/>
       <c r="C75" s="38">
@@ -14784,7 +14766,7 @@
       <c r="J75" s="29"/>
       <c r="K75" s="29"/>
     </row>
-    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="29"/>
       <c r="B76" s="27"/>
       <c r="C76" s="35">
@@ -14805,7 +14787,7 @@
       <c r="J76" s="29"/>
       <c r="K76" s="29"/>
     </row>
-    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="29"/>
       <c r="B77" s="27"/>
       <c r="C77" s="38">
@@ -14826,7 +14808,7 @@
       <c r="J77" s="29"/>
       <c r="K77" s="29"/>
     </row>
-    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="29"/>
       <c r="B78" s="27"/>
       <c r="C78" s="35">
@@ -14847,7 +14829,7 @@
       <c r="J78" s="29"/>
       <c r="K78" s="29"/>
     </row>
-    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="29"/>
       <c r="B79" s="27"/>
       <c r="C79" s="38">
@@ -14868,7 +14850,7 @@
       <c r="J79" s="29"/>
       <c r="K79" s="29"/>
     </row>
-    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="29"/>
       <c r="B80" s="27"/>
       <c r="C80" s="35">
@@ -14889,7 +14871,7 @@
       <c r="J80" s="29"/>
       <c r="K80" s="29"/>
     </row>
-    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="29"/>
       <c r="B81" s="27"/>
       <c r="C81" s="38">
@@ -14910,7 +14892,7 @@
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
     </row>
-    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="29"/>
       <c r="B82" s="27"/>
       <c r="C82" s="35">
@@ -14931,7 +14913,7 @@
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
     </row>
-    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="29"/>
       <c r="B83" s="27"/>
       <c r="C83" s="38">
@@ -14952,7 +14934,7 @@
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
     </row>
-    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="29"/>
       <c r="B84" s="27"/>
       <c r="C84" s="35">
@@ -14973,7 +14955,7 @@
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
     </row>
-    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="29"/>
       <c r="B85" s="27"/>
       <c r="C85" s="38">
@@ -14994,7 +14976,7 @@
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
     </row>
-    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="29"/>
       <c r="B86" s="27"/>
       <c r="C86" s="35">
@@ -15015,7 +14997,7 @@
       <c r="J86" s="29"/>
       <c r="K86" s="29"/>
     </row>
-    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="29"/>
       <c r="B87" s="27"/>
       <c r="C87" s="38">
@@ -15036,7 +15018,7 @@
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
     </row>
-    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="29"/>
       <c r="B88" s="27"/>
       <c r="C88" s="35">
@@ -15057,7 +15039,7 @@
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
     </row>
-    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="29"/>
       <c r="B89" s="27"/>
       <c r="C89" s="38">
@@ -15078,7 +15060,7 @@
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
     </row>
-    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="29"/>
       <c r="B90" s="27"/>
       <c r="C90" s="35">
@@ -15099,7 +15081,7 @@
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
     </row>
-    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="29"/>
       <c r="B91" s="27"/>
       <c r="C91" s="38">
@@ -15120,7 +15102,7 @@
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
     </row>
-    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="29"/>
       <c r="B92" s="27"/>
       <c r="C92" s="35">
@@ -15141,7 +15123,7 @@
       <c r="J92" s="29"/>
       <c r="K92" s="29"/>
     </row>
-    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="29"/>
       <c r="B93" s="27"/>
       <c r="C93" s="38">
@@ -15162,7 +15144,7 @@
       <c r="J93" s="29"/>
       <c r="K93" s="29"/>
     </row>
-    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="29"/>
       <c r="B94" s="27"/>
       <c r="C94" s="35">
@@ -15183,7 +15165,7 @@
       <c r="J94" s="29"/>
       <c r="K94" s="29"/>
     </row>
-    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="29"/>
       <c r="B95" s="27"/>
       <c r="C95" s="38">
@@ -15204,7 +15186,7 @@
       <c r="J95" s="29"/>
       <c r="K95" s="29"/>
     </row>
-    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="29"/>
       <c r="B96" s="27"/>
       <c r="C96" s="35">
@@ -15225,7 +15207,7 @@
       <c r="J96" s="29"/>
       <c r="K96" s="29"/>
     </row>
-    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="29"/>
       <c r="B97" s="27"/>
       <c r="C97" s="38">
@@ -15246,7 +15228,7 @@
       <c r="J97" s="29"/>
       <c r="K97" s="29"/>
     </row>
-    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="29"/>
       <c r="B98" s="27"/>
       <c r="C98" s="35">
@@ -15267,7 +15249,7 @@
       <c r="J98" s="29"/>
       <c r="K98" s="29"/>
     </row>
-    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="29"/>
       <c r="B99" s="27"/>
       <c r="C99" s="38">
@@ -15288,7 +15270,7 @@
       <c r="J99" s="29"/>
       <c r="K99" s="29"/>
     </row>
-    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="29"/>
       <c r="B100" s="27"/>
       <c r="C100" s="35">
@@ -15309,7 +15291,7 @@
       <c r="J100" s="29"/>
       <c r="K100" s="29"/>
     </row>
-    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="29"/>
       <c r="B101" s="27"/>
       <c r="C101" s="38">
@@ -15330,7 +15312,7 @@
       <c r="J101" s="29"/>
       <c r="K101" s="29"/>
     </row>
-    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="29"/>
       <c r="B102" s="27"/>
       <c r="C102" s="35">
@@ -15351,7 +15333,7 @@
       <c r="J102" s="29"/>
       <c r="K102" s="29"/>
     </row>
-    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="29"/>
       <c r="B103" s="27"/>
       <c r="C103" s="38">
@@ -15372,7 +15354,7 @@
       <c r="J103" s="29"/>
       <c r="K103" s="29"/>
     </row>
-    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="29"/>
       <c r="B104" s="27"/>
       <c r="C104" s="35">
@@ -15393,7 +15375,7 @@
       <c r="J104" s="29"/>
       <c r="K104" s="29"/>
     </row>
-    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="29"/>
       <c r="B105" s="27"/>
       <c r="C105" s="38">
@@ -15414,7 +15396,7 @@
       <c r="J105" s="29"/>
       <c r="K105" s="29"/>
     </row>
-    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="29"/>
       <c r="B106" s="27"/>
       <c r="C106" s="35">
@@ -15435,7 +15417,7 @@
       <c r="J106" s="29"/>
       <c r="K106" s="29"/>
     </row>
-    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="29"/>
       <c r="B107" s="27"/>
       <c r="C107" s="38">
@@ -15456,7 +15438,7 @@
       <c r="J107" s="29"/>
       <c r="K107" s="29"/>
     </row>
-    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="29"/>
       <c r="B108" s="27"/>
       <c r="C108" s="35">
@@ -15477,7 +15459,7 @@
       <c r="J108" s="29"/>
       <c r="K108" s="29"/>
     </row>
-    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="29"/>
       <c r="B109" s="27"/>
       <c r="C109" s="38">
@@ -15498,7 +15480,7 @@
       <c r="J109" s="29"/>
       <c r="K109" s="29"/>
     </row>
-    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="29"/>
       <c r="B110" s="27"/>
       <c r="C110" s="35">
@@ -15519,7 +15501,7 @@
       <c r="J110" s="29"/>
       <c r="K110" s="29"/>
     </row>
-    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="29"/>
       <c r="B111" s="27"/>
       <c r="C111" s="38">
@@ -15540,7 +15522,7 @@
       <c r="J111" s="29"/>
       <c r="K111" s="29"/>
     </row>
-    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="29"/>
       <c r="B112" s="27"/>
       <c r="C112" s="35">
@@ -15561,7 +15543,7 @@
       <c r="J112" s="29"/>
       <c r="K112" s="29"/>
     </row>
-    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="29"/>
       <c r="B113" s="27"/>
       <c r="C113" s="38">
@@ -15582,7 +15564,7 @@
       <c r="J113" s="29"/>
       <c r="K113" s="29"/>
     </row>
-    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="29"/>
       <c r="B114" s="27"/>
       <c r="C114" s="35">
@@ -15603,7 +15585,7 @@
       <c r="J114" s="29"/>
       <c r="K114" s="29"/>
     </row>
-    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="29"/>
       <c r="B115" s="27"/>
       <c r="C115" s="38">
@@ -15624,7 +15606,7 @@
       <c r="J115" s="29"/>
       <c r="K115" s="29"/>
     </row>
-    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="29"/>
       <c r="B116" s="27"/>
       <c r="C116" s="35">
@@ -15645,7 +15627,7 @@
       <c r="J116" s="29"/>
       <c r="K116" s="29"/>
     </row>
-    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="29"/>
       <c r="B117" s="27"/>
       <c r="C117" s="38">
@@ -15666,7 +15648,7 @@
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
     </row>
-    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="29"/>
       <c r="B118" s="27"/>
       <c r="C118" s="35">
@@ -15687,7 +15669,7 @@
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
     </row>
-    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="29"/>
       <c r="B119" s="27"/>
       <c r="C119" s="38">
@@ -15708,7 +15690,7 @@
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
     </row>
-    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="29"/>
       <c r="B120" s="27"/>
       <c r="C120" s="35">
@@ -15729,7 +15711,7 @@
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
     </row>
-    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="29"/>
       <c r="B121" s="27"/>
       <c r="C121" s="38">
@@ -15750,7 +15732,7 @@
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
     </row>
-    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="29"/>
       <c r="B122" s="27"/>
       <c r="C122" s="35">
@@ -15771,7 +15753,7 @@
       <c r="J122" s="29"/>
       <c r="K122" s="29"/>
     </row>
-    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="29"/>
       <c r="B123" s="27"/>
       <c r="C123" s="38">
@@ -15792,7 +15774,7 @@
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
     </row>
-    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="29"/>
       <c r="B124" s="27"/>
       <c r="C124" s="35">
@@ -15813,7 +15795,7 @@
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
     </row>
-    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="29"/>
       <c r="B125" s="27"/>
       <c r="C125" s="38">
@@ -15834,7 +15816,7 @@
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
     </row>
-    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="29"/>
       <c r="B126" s="27"/>
       <c r="C126" s="35">
@@ -15855,7 +15837,7 @@
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
     </row>
-    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="29"/>
       <c r="B127" s="27"/>
       <c r="C127" s="38">
@@ -15876,7 +15858,7 @@
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
     </row>
-    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="29"/>
       <c r="B128" s="27"/>
       <c r="C128" s="35">
@@ -15897,7 +15879,7 @@
       <c r="J128" s="29"/>
       <c r="K128" s="29"/>
     </row>
-    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="29"/>
       <c r="B129" s="27"/>
       <c r="C129" s="38">
@@ -15918,7 +15900,7 @@
       <c r="J129" s="29"/>
       <c r="K129" s="29"/>
     </row>
-    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="29"/>
       <c r="B130" s="27"/>
       <c r="C130" s="35">
@@ -15939,7 +15921,7 @@
       <c r="J130" s="29"/>
       <c r="K130" s="29"/>
     </row>
-    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="29"/>
       <c r="B131" s="27"/>
       <c r="C131" s="38">
@@ -15960,7 +15942,7 @@
       <c r="J131" s="29"/>
       <c r="K131" s="29"/>
     </row>
-    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="29"/>
       <c r="B132" s="27"/>
       <c r="C132" s="35">
@@ -15981,7 +15963,7 @@
       <c r="J132" s="29"/>
       <c r="K132" s="29"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="38">
         <v>76</v>
       </c>
@@ -15995,7 +15977,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="35">
         <v>77</v>
       </c>
@@ -16009,7 +15991,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -16023,7 +16005,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="3">
         <v>79</v>
       </c>
@@ -16060,29 +16042,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R136"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>259</v>
       </c>
@@ -16090,7 +16072,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="24" t="s">
         <v>226</v>
       </c>
@@ -16098,7 +16080,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>227</v>
@@ -16106,7 +16088,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>16</v>
@@ -16114,13 +16096,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="26" t="s">
         <v>227</v>
       </c>
@@ -16128,7 +16110,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>7</v>
@@ -16143,7 +16125,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -16157,7 +16139,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -16171,7 +16153,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -16185,7 +16167,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -16199,7 +16181,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -16213,7 +16195,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -16227,7 +16209,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -16241,7 +16223,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -16255,7 +16237,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -16269,7 +16251,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -16283,7 +16265,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -16297,7 +16279,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -16311,7 +16293,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -16325,7 +16307,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -16339,7 +16321,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -16353,7 +16335,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -16367,7 +16349,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -16381,7 +16363,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -16395,7 +16377,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -16409,7 +16391,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -16423,7 +16405,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -16437,7 +16419,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -16451,7 +16433,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -16465,7 +16447,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -16479,7 +16461,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -16493,7 +16475,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -16507,7 +16489,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -16521,7 +16503,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -16535,7 +16517,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -16549,7 +16531,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -16563,7 +16545,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -16577,7 +16559,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -16591,7 +16573,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -16605,7 +16587,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -16619,7 +16601,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -16633,7 +16615,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -16647,7 +16629,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -16661,7 +16643,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -16675,7 +16657,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -16689,7 +16671,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -16703,7 +16685,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -16717,7 +16699,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -16731,7 +16713,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -16745,7 +16727,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -16759,7 +16741,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -16773,7 +16755,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -16787,12 +16769,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="33" t="s">
         <v>7</v>
       </c>
@@ -16806,7 +16788,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="35">
         <v>1</v>
       </c>
@@ -16820,7 +16802,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="38">
         <v>2</v>
       </c>
@@ -16834,7 +16816,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="35">
         <v>3</v>
       </c>
@@ -16848,7 +16830,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="38">
         <v>4</v>
       </c>
@@ -16862,7 +16844,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="35">
         <v>5</v>
       </c>
@@ -16876,7 +16858,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="38">
         <v>6</v>
       </c>
@@ -16890,7 +16872,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="29"/>
       <c r="B64" s="27"/>
       <c r="C64" s="35">
@@ -16911,7 +16893,7 @@
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
     </row>
-    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="29"/>
       <c r="B65" s="27"/>
       <c r="C65" s="38">
@@ -16932,7 +16914,7 @@
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
     </row>
-    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="29"/>
       <c r="B66" s="27"/>
       <c r="C66" s="35">
@@ -16953,7 +16935,7 @@
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
     </row>
-    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="29"/>
       <c r="B67" s="27"/>
       <c r="C67" s="38">
@@ -16974,7 +16956,7 @@
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
     </row>
-    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="29"/>
       <c r="B68" s="27"/>
       <c r="C68" s="35">
@@ -16995,7 +16977,7 @@
       <c r="J68" s="29"/>
       <c r="K68" s="29"/>
     </row>
-    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="29"/>
       <c r="B69" s="27"/>
       <c r="C69" s="38">
@@ -17016,7 +16998,7 @@
       <c r="J69" s="29"/>
       <c r="K69" s="29"/>
     </row>
-    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="29"/>
       <c r="B70" s="27"/>
       <c r="C70" s="35">
@@ -17037,7 +17019,7 @@
       <c r="J70" s="29"/>
       <c r="K70" s="29"/>
     </row>
-    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="29"/>
       <c r="B71" s="27"/>
       <c r="C71" s="38">
@@ -17058,7 +17040,7 @@
       <c r="J71" s="29"/>
       <c r="K71" s="29"/>
     </row>
-    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="29"/>
       <c r="B72" s="27"/>
       <c r="C72" s="35">
@@ -17079,7 +17061,7 @@
       <c r="J72" s="29"/>
       <c r="K72" s="29"/>
     </row>
-    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="29"/>
       <c r="B73" s="27"/>
       <c r="C73" s="38">
@@ -17100,7 +17082,7 @@
       <c r="J73" s="29"/>
       <c r="K73" s="29"/>
     </row>
-    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="29"/>
       <c r="B74" s="27"/>
       <c r="C74" s="35">
@@ -17121,7 +17103,7 @@
       <c r="J74" s="29"/>
       <c r="K74" s="29"/>
     </row>
-    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="29"/>
       <c r="B75" s="27"/>
       <c r="C75" s="38">
@@ -17142,7 +17124,7 @@
       <c r="J75" s="29"/>
       <c r="K75" s="29"/>
     </row>
-    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="29"/>
       <c r="B76" s="27"/>
       <c r="C76" s="35">
@@ -17163,7 +17145,7 @@
       <c r="J76" s="29"/>
       <c r="K76" s="29"/>
     </row>
-    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="29"/>
       <c r="B77" s="27"/>
       <c r="C77" s="38">
@@ -17184,7 +17166,7 @@
       <c r="J77" s="29"/>
       <c r="K77" s="29"/>
     </row>
-    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="29"/>
       <c r="B78" s="27"/>
       <c r="C78" s="35">
@@ -17205,7 +17187,7 @@
       <c r="J78" s="29"/>
       <c r="K78" s="29"/>
     </row>
-    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="29"/>
       <c r="B79" s="27"/>
       <c r="C79" s="38">
@@ -17226,7 +17208,7 @@
       <c r="J79" s="29"/>
       <c r="K79" s="29"/>
     </row>
-    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="29"/>
       <c r="B80" s="27"/>
       <c r="C80" s="35">
@@ -17247,7 +17229,7 @@
       <c r="J80" s="29"/>
       <c r="K80" s="29"/>
     </row>
-    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="29"/>
       <c r="B81" s="27"/>
       <c r="C81" s="38">
@@ -17268,7 +17250,7 @@
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
     </row>
-    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="29"/>
       <c r="B82" s="27"/>
       <c r="C82" s="35">
@@ -17289,7 +17271,7 @@
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
     </row>
-    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="29"/>
       <c r="B83" s="27"/>
       <c r="C83" s="38">
@@ -17310,7 +17292,7 @@
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
     </row>
-    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="29"/>
       <c r="B84" s="27"/>
       <c r="C84" s="35">
@@ -17331,7 +17313,7 @@
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
     </row>
-    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="29"/>
       <c r="B85" s="27"/>
       <c r="C85" s="38">
@@ -17352,7 +17334,7 @@
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
     </row>
-    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="29"/>
       <c r="B86" s="27"/>
       <c r="C86" s="35">
@@ -17373,7 +17355,7 @@
       <c r="J86" s="29"/>
       <c r="K86" s="29"/>
     </row>
-    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="29"/>
       <c r="B87" s="27"/>
       <c r="C87" s="38">
@@ -17394,7 +17376,7 @@
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
     </row>
-    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="29"/>
       <c r="B88" s="27"/>
       <c r="C88" s="35">
@@ -17415,7 +17397,7 @@
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
     </row>
-    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="29"/>
       <c r="B89" s="27"/>
       <c r="C89" s="38">
@@ -17436,7 +17418,7 @@
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
     </row>
-    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="29"/>
       <c r="B90" s="27"/>
       <c r="C90" s="35">
@@ -17457,7 +17439,7 @@
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
     </row>
-    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="29"/>
       <c r="B91" s="27"/>
       <c r="C91" s="38">
@@ -17478,7 +17460,7 @@
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
     </row>
-    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="29"/>
       <c r="B92" s="27"/>
       <c r="C92" s="35">
@@ -17499,7 +17481,7 @@
       <c r="J92" s="29"/>
       <c r="K92" s="29"/>
     </row>
-    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="29"/>
       <c r="B93" s="27"/>
       <c r="C93" s="38">
@@ -17520,7 +17502,7 @@
       <c r="J93" s="29"/>
       <c r="K93" s="29"/>
     </row>
-    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="29"/>
       <c r="B94" s="27"/>
       <c r="C94" s="35">
@@ -17541,7 +17523,7 @@
       <c r="J94" s="29"/>
       <c r="K94" s="29"/>
     </row>
-    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="29"/>
       <c r="B95" s="27"/>
       <c r="C95" s="38">
@@ -17562,7 +17544,7 @@
       <c r="J95" s="29"/>
       <c r="K95" s="29"/>
     </row>
-    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="29"/>
       <c r="B96" s="27"/>
       <c r="C96" s="35">
@@ -17583,7 +17565,7 @@
       <c r="J96" s="29"/>
       <c r="K96" s="29"/>
     </row>
-    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="29"/>
       <c r="B97" s="27"/>
       <c r="C97" s="38">
@@ -17604,7 +17586,7 @@
       <c r="J97" s="29"/>
       <c r="K97" s="29"/>
     </row>
-    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="29"/>
       <c r="B98" s="27"/>
       <c r="C98" s="35">
@@ -17625,7 +17607,7 @@
       <c r="J98" s="29"/>
       <c r="K98" s="29"/>
     </row>
-    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="29"/>
       <c r="B99" s="27"/>
       <c r="C99" s="38">
@@ -17646,7 +17628,7 @@
       <c r="J99" s="29"/>
       <c r="K99" s="29"/>
     </row>
-    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="29"/>
       <c r="B100" s="27"/>
       <c r="C100" s="35">
@@ -17667,7 +17649,7 @@
       <c r="J100" s="29"/>
       <c r="K100" s="29"/>
     </row>
-    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="29"/>
       <c r="B101" s="27"/>
       <c r="C101" s="38">
@@ -17688,7 +17670,7 @@
       <c r="J101" s="29"/>
       <c r="K101" s="29"/>
     </row>
-    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="29"/>
       <c r="B102" s="27"/>
       <c r="C102" s="35">
@@ -17709,7 +17691,7 @@
       <c r="J102" s="29"/>
       <c r="K102" s="29"/>
     </row>
-    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="29"/>
       <c r="B103" s="27"/>
       <c r="C103" s="38">
@@ -17730,7 +17712,7 @@
       <c r="J103" s="29"/>
       <c r="K103" s="29"/>
     </row>
-    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="29"/>
       <c r="B104" s="27"/>
       <c r="C104" s="35">
@@ -17751,7 +17733,7 @@
       <c r="J104" s="29"/>
       <c r="K104" s="29"/>
     </row>
-    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="29"/>
       <c r="B105" s="27"/>
       <c r="C105" s="38">
@@ -17772,7 +17754,7 @@
       <c r="J105" s="29"/>
       <c r="K105" s="29"/>
     </row>
-    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="29"/>
       <c r="B106" s="27"/>
       <c r="C106" s="35">
@@ -17793,7 +17775,7 @@
       <c r="J106" s="29"/>
       <c r="K106" s="29"/>
     </row>
-    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="29"/>
       <c r="B107" s="27"/>
       <c r="C107" s="38">
@@ -17814,7 +17796,7 @@
       <c r="J107" s="29"/>
       <c r="K107" s="29"/>
     </row>
-    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="29"/>
       <c r="B108" s="27"/>
       <c r="C108" s="35">
@@ -17835,7 +17817,7 @@
       <c r="J108" s="29"/>
       <c r="K108" s="29"/>
     </row>
-    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="29"/>
       <c r="B109" s="27"/>
       <c r="C109" s="38">
@@ -17856,7 +17838,7 @@
       <c r="J109" s="29"/>
       <c r="K109" s="29"/>
     </row>
-    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="29"/>
       <c r="B110" s="27"/>
       <c r="C110" s="35">
@@ -17877,7 +17859,7 @@
       <c r="J110" s="29"/>
       <c r="K110" s="29"/>
     </row>
-    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="29"/>
       <c r="B111" s="27"/>
       <c r="C111" s="38">
@@ -17898,7 +17880,7 @@
       <c r="J111" s="29"/>
       <c r="K111" s="29"/>
     </row>
-    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="29"/>
       <c r="B112" s="27"/>
       <c r="C112" s="35">
@@ -17919,7 +17901,7 @@
       <c r="J112" s="29"/>
       <c r="K112" s="29"/>
     </row>
-    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="29"/>
       <c r="B113" s="27"/>
       <c r="C113" s="38">
@@ -17940,7 +17922,7 @@
       <c r="J113" s="29"/>
       <c r="K113" s="29"/>
     </row>
-    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="29"/>
       <c r="B114" s="27"/>
       <c r="C114" s="35">
@@ -17961,7 +17943,7 @@
       <c r="J114" s="29"/>
       <c r="K114" s="29"/>
     </row>
-    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="29"/>
       <c r="B115" s="27"/>
       <c r="C115" s="38">
@@ -17982,7 +17964,7 @@
       <c r="J115" s="29"/>
       <c r="K115" s="29"/>
     </row>
-    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="29"/>
       <c r="B116" s="27"/>
       <c r="C116" s="35">
@@ -18003,7 +17985,7 @@
       <c r="J116" s="29"/>
       <c r="K116" s="29"/>
     </row>
-    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="29"/>
       <c r="B117" s="27"/>
       <c r="C117" s="38">
@@ -18024,7 +18006,7 @@
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
     </row>
-    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="29"/>
       <c r="B118" s="27"/>
       <c r="C118" s="35">
@@ -18045,7 +18027,7 @@
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
     </row>
-    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="29"/>
       <c r="B119" s="27"/>
       <c r="C119" s="38">
@@ -18066,7 +18048,7 @@
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
     </row>
-    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="29"/>
       <c r="B120" s="27"/>
       <c r="C120" s="35">
@@ -18087,7 +18069,7 @@
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
     </row>
-    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="29"/>
       <c r="B121" s="27"/>
       <c r="C121" s="38">
@@ -18108,7 +18090,7 @@
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
     </row>
-    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="29"/>
       <c r="B122" s="27"/>
       <c r="C122" s="35">
@@ -18129,7 +18111,7 @@
       <c r="J122" s="29"/>
       <c r="K122" s="29"/>
     </row>
-    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="29"/>
       <c r="B123" s="27"/>
       <c r="C123" s="38">
@@ -18150,7 +18132,7 @@
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
     </row>
-    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="29"/>
       <c r="B124" s="27"/>
       <c r="C124" s="35">
@@ -18171,7 +18153,7 @@
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
     </row>
-    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="29"/>
       <c r="B125" s="27"/>
       <c r="C125" s="38">
@@ -18192,7 +18174,7 @@
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
     </row>
-    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="29"/>
       <c r="B126" s="27"/>
       <c r="C126" s="35">
@@ -18213,7 +18195,7 @@
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
     </row>
-    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="29"/>
       <c r="B127" s="27"/>
       <c r="C127" s="38">
@@ -18234,7 +18216,7 @@
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
     </row>
-    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="29"/>
       <c r="B128" s="27"/>
       <c r="C128" s="35">
@@ -18255,7 +18237,7 @@
       <c r="J128" s="29"/>
       <c r="K128" s="29"/>
     </row>
-    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="29"/>
       <c r="B129" s="27"/>
       <c r="C129" s="38">
@@ -18276,7 +18258,7 @@
       <c r="J129" s="29"/>
       <c r="K129" s="29"/>
     </row>
-    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="29"/>
       <c r="B130" s="27"/>
       <c r="C130" s="35">
@@ -18297,7 +18279,7 @@
       <c r="J130" s="29"/>
       <c r="K130" s="29"/>
     </row>
-    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="29"/>
       <c r="B131" s="27"/>
       <c r="C131" s="38">
@@ -18318,7 +18300,7 @@
       <c r="J131" s="29"/>
       <c r="K131" s="29"/>
     </row>
-    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="29"/>
       <c r="B132" s="27"/>
       <c r="C132" s="35">
@@ -18339,7 +18321,7 @@
       <c r="J132" s="29"/>
       <c r="K132" s="29"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="38">
         <v>76</v>
       </c>
@@ -18353,7 +18335,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="35">
         <v>77</v>
       </c>
@@ -18367,7 +18349,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -18381,7 +18363,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="3">
         <v>79</v>
       </c>
@@ -18418,29 +18400,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R136"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="29" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="32" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="32" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="29" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="29" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="27" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="32" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="29" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="29" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="29" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="29" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="29" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="29" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>260</v>
       </c>
@@ -18448,7 +18430,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="24" t="s">
         <v>226</v>
       </c>
@@ -18456,7 +18438,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="25"/>
     </row>
-    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="26"/>
       <c r="D4" s="26" t="s">
         <v>227</v>
@@ -18464,7 +18446,7 @@
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
     </row>
-    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="26"/>
       <c r="D5" s="26" t="s">
         <v>16</v>
@@ -18472,13 +18454,13 @@
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="26"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
     </row>
-    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="23" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="26" t="s">
         <v>227</v>
       </c>
@@ -18486,7 +18468,7 @@
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="7"/>
       <c r="C8" s="11" t="s">
         <v>7</v>
@@ -18501,7 +18483,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -18515,7 +18497,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -18529,7 +18511,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -18543,7 +18525,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -18557,7 +18539,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -18571,7 +18553,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -18585,7 +18567,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -18599,7 +18581,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -18613,7 +18595,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -18627,7 +18609,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -18641,7 +18623,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -18655,7 +18637,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -18669,7 +18651,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -18683,7 +18665,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -18697,7 +18679,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -18711,7 +18693,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -18725,7 +18707,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -18739,7 +18721,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -18753,7 +18735,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -18767,7 +18749,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -18781,7 +18763,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -18795,7 +18777,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -18809,7 +18791,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -18823,7 +18805,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="27" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -18837,7 +18819,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -18851,7 +18833,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -18865,7 +18847,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -18879,7 +18861,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -18893,7 +18875,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -18907,7 +18889,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -18921,7 +18903,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -18935,7 +18917,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -18949,7 +18931,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -18963,7 +18945,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -18977,7 +18959,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -18991,7 +18973,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -19005,7 +18987,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -19019,7 +19001,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -19033,7 +19015,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -19047,7 +19029,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -19061,7 +19043,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -19075,7 +19057,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -19089,7 +19071,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -19103,7 +19085,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -19117,7 +19099,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -19131,7 +19113,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -19145,12 +19127,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="33" t="s">
         <v>7</v>
       </c>
@@ -19164,7 +19146,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="35">
         <v>1</v>
       </c>
@@ -19178,7 +19160,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="38">
         <v>2</v>
       </c>
@@ -19192,7 +19174,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="35">
         <v>3</v>
       </c>
@@ -19206,7 +19188,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="38">
         <v>4</v>
       </c>
@@ -19220,7 +19202,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="35">
         <v>5</v>
       </c>
@@ -19234,7 +19216,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="38">
         <v>6</v>
       </c>
@@ -19248,7 +19230,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="29"/>
       <c r="B64" s="27"/>
       <c r="C64" s="35">
@@ -19269,7 +19251,7 @@
       <c r="J64" s="29"/>
       <c r="K64" s="29"/>
     </row>
-    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="29"/>
       <c r="B65" s="27"/>
       <c r="C65" s="38">
@@ -19290,7 +19272,7 @@
       <c r="J65" s="29"/>
       <c r="K65" s="29"/>
     </row>
-    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="29"/>
       <c r="B66" s="27"/>
       <c r="C66" s="35">
@@ -19311,7 +19293,7 @@
       <c r="J66" s="29"/>
       <c r="K66" s="29"/>
     </row>
-    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="29"/>
       <c r="B67" s="27"/>
       <c r="C67" s="38">
@@ -19332,7 +19314,7 @@
       <c r="J67" s="29"/>
       <c r="K67" s="29"/>
     </row>
-    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="29"/>
       <c r="B68" s="27"/>
       <c r="C68" s="35">
@@ -19353,7 +19335,7 @@
       <c r="J68" s="29"/>
       <c r="K68" s="29"/>
     </row>
-    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="29"/>
       <c r="B69" s="27"/>
       <c r="C69" s="38">
@@ -19374,7 +19356,7 @@
       <c r="J69" s="29"/>
       <c r="K69" s="29"/>
     </row>
-    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="29"/>
       <c r="B70" s="27"/>
       <c r="C70" s="35">
@@ -19395,7 +19377,7 @@
       <c r="J70" s="29"/>
       <c r="K70" s="29"/>
     </row>
-    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="29"/>
       <c r="B71" s="27"/>
       <c r="C71" s="38">
@@ -19416,7 +19398,7 @@
       <c r="J71" s="29"/>
       <c r="K71" s="29"/>
     </row>
-    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="29"/>
       <c r="B72" s="27"/>
       <c r="C72" s="35">
@@ -19437,7 +19419,7 @@
       <c r="J72" s="29"/>
       <c r="K72" s="29"/>
     </row>
-    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="29"/>
       <c r="B73" s="27"/>
       <c r="C73" s="38">
@@ -19458,7 +19440,7 @@
       <c r="J73" s="29"/>
       <c r="K73" s="29"/>
     </row>
-    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="29"/>
       <c r="B74" s="27"/>
       <c r="C74" s="35">
@@ -19479,7 +19461,7 @@
       <c r="J74" s="29"/>
       <c r="K74" s="29"/>
     </row>
-    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="29"/>
       <c r="B75" s="27"/>
       <c r="C75" s="38">
@@ -19500,7 +19482,7 @@
       <c r="J75" s="29"/>
       <c r="K75" s="29"/>
     </row>
-    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="29"/>
       <c r="B76" s="27"/>
       <c r="C76" s="35">
@@ -19521,7 +19503,7 @@
       <c r="J76" s="29"/>
       <c r="K76" s="29"/>
     </row>
-    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="29"/>
       <c r="B77" s="27"/>
       <c r="C77" s="38">
@@ -19542,7 +19524,7 @@
       <c r="J77" s="29"/>
       <c r="K77" s="29"/>
     </row>
-    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="29"/>
       <c r="B78" s="27"/>
       <c r="C78" s="35">
@@ -19563,7 +19545,7 @@
       <c r="J78" s="29"/>
       <c r="K78" s="29"/>
     </row>
-    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="29"/>
       <c r="B79" s="27"/>
       <c r="C79" s="38">
@@ -19584,7 +19566,7 @@
       <c r="J79" s="29"/>
       <c r="K79" s="29"/>
     </row>
-    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="29"/>
       <c r="B80" s="27"/>
       <c r="C80" s="35">
@@ -19605,7 +19587,7 @@
       <c r="J80" s="29"/>
       <c r="K80" s="29"/>
     </row>
-    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="29"/>
       <c r="B81" s="27"/>
       <c r="C81" s="38">
@@ -19626,7 +19608,7 @@
       <c r="J81" s="29"/>
       <c r="K81" s="29"/>
     </row>
-    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="29"/>
       <c r="B82" s="27"/>
       <c r="C82" s="35">
@@ -19647,7 +19629,7 @@
       <c r="J82" s="29"/>
       <c r="K82" s="29"/>
     </row>
-    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="29"/>
       <c r="B83" s="27"/>
       <c r="C83" s="38">
@@ -19668,7 +19650,7 @@
       <c r="J83" s="29"/>
       <c r="K83" s="29"/>
     </row>
-    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="29"/>
       <c r="B84" s="27"/>
       <c r="C84" s="35">
@@ -19689,7 +19671,7 @@
       <c r="J84" s="29"/>
       <c r="K84" s="29"/>
     </row>
-    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="29"/>
       <c r="B85" s="27"/>
       <c r="C85" s="38">
@@ -19710,7 +19692,7 @@
       <c r="J85" s="29"/>
       <c r="K85" s="29"/>
     </row>
-    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="29"/>
       <c r="B86" s="27"/>
       <c r="C86" s="35">
@@ -19731,7 +19713,7 @@
       <c r="J86" s="29"/>
       <c r="K86" s="29"/>
     </row>
-    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="29"/>
       <c r="B87" s="27"/>
       <c r="C87" s="38">
@@ -19752,7 +19734,7 @@
       <c r="J87" s="29"/>
       <c r="K87" s="29"/>
     </row>
-    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="29"/>
       <c r="B88" s="27"/>
       <c r="C88" s="35">
@@ -19773,7 +19755,7 @@
       <c r="J88" s="29"/>
       <c r="K88" s="29"/>
     </row>
-    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="29"/>
       <c r="B89" s="27"/>
       <c r="C89" s="38">
@@ -19794,7 +19776,7 @@
       <c r="J89" s="29"/>
       <c r="K89" s="29"/>
     </row>
-    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="29"/>
       <c r="B90" s="27"/>
       <c r="C90" s="35">
@@ -19815,7 +19797,7 @@
       <c r="J90" s="29"/>
       <c r="K90" s="29"/>
     </row>
-    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="29"/>
       <c r="B91" s="27"/>
       <c r="C91" s="38">
@@ -19836,7 +19818,7 @@
       <c r="J91" s="29"/>
       <c r="K91" s="29"/>
     </row>
-    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="29"/>
       <c r="B92" s="27"/>
       <c r="C92" s="35">
@@ -19857,7 +19839,7 @@
       <c r="J92" s="29"/>
       <c r="K92" s="29"/>
     </row>
-    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="29"/>
       <c r="B93" s="27"/>
       <c r="C93" s="38">
@@ -19878,7 +19860,7 @@
       <c r="J93" s="29"/>
       <c r="K93" s="29"/>
     </row>
-    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="29"/>
       <c r="B94" s="27"/>
       <c r="C94" s="35">
@@ -19899,7 +19881,7 @@
       <c r="J94" s="29"/>
       <c r="K94" s="29"/>
     </row>
-    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="29"/>
       <c r="B95" s="27"/>
       <c r="C95" s="38">
@@ -19920,7 +19902,7 @@
       <c r="J95" s="29"/>
       <c r="K95" s="29"/>
     </row>
-    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="29"/>
       <c r="B96" s="27"/>
       <c r="C96" s="35">
@@ -19941,7 +19923,7 @@
       <c r="J96" s="29"/>
       <c r="K96" s="29"/>
     </row>
-    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="29"/>
       <c r="B97" s="27"/>
       <c r="C97" s="38">
@@ -19962,7 +19944,7 @@
       <c r="J97" s="29"/>
       <c r="K97" s="29"/>
     </row>
-    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="29"/>
       <c r="B98" s="27"/>
       <c r="C98" s="35">
@@ -19983,7 +19965,7 @@
       <c r="J98" s="29"/>
       <c r="K98" s="29"/>
     </row>
-    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="29"/>
       <c r="B99" s="27"/>
       <c r="C99" s="38">
@@ -20004,7 +19986,7 @@
       <c r="J99" s="29"/>
       <c r="K99" s="29"/>
     </row>
-    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="29"/>
       <c r="B100" s="27"/>
       <c r="C100" s="35">
@@ -20025,7 +20007,7 @@
       <c r="J100" s="29"/>
       <c r="K100" s="29"/>
     </row>
-    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="29"/>
       <c r="B101" s="27"/>
       <c r="C101" s="38">
@@ -20046,7 +20028,7 @@
       <c r="J101" s="29"/>
       <c r="K101" s="29"/>
     </row>
-    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="29"/>
       <c r="B102" s="27"/>
       <c r="C102" s="35">
@@ -20067,7 +20049,7 @@
       <c r="J102" s="29"/>
       <c r="K102" s="29"/>
     </row>
-    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="29"/>
       <c r="B103" s="27"/>
       <c r="C103" s="38">
@@ -20088,7 +20070,7 @@
       <c r="J103" s="29"/>
       <c r="K103" s="29"/>
     </row>
-    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="29"/>
       <c r="B104" s="27"/>
       <c r="C104" s="35">
@@ -20109,7 +20091,7 @@
       <c r="J104" s="29"/>
       <c r="K104" s="29"/>
     </row>
-    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="29"/>
       <c r="B105" s="27"/>
       <c r="C105" s="38">
@@ -20130,7 +20112,7 @@
       <c r="J105" s="29"/>
       <c r="K105" s="29"/>
     </row>
-    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="29"/>
       <c r="B106" s="27"/>
       <c r="C106" s="35">
@@ -20151,7 +20133,7 @@
       <c r="J106" s="29"/>
       <c r="K106" s="29"/>
     </row>
-    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="29"/>
       <c r="B107" s="27"/>
       <c r="C107" s="38">
@@ -20172,7 +20154,7 @@
       <c r="J107" s="29"/>
       <c r="K107" s="29"/>
     </row>
-    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="29"/>
       <c r="B108" s="27"/>
       <c r="C108" s="35">
@@ -20193,7 +20175,7 @@
       <c r="J108" s="29"/>
       <c r="K108" s="29"/>
     </row>
-    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="29"/>
       <c r="B109" s="27"/>
       <c r="C109" s="38">
@@ -20214,7 +20196,7 @@
       <c r="J109" s="29"/>
       <c r="K109" s="29"/>
     </row>
-    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="29"/>
       <c r="B110" s="27"/>
       <c r="C110" s="35">
@@ -20235,7 +20217,7 @@
       <c r="J110" s="29"/>
       <c r="K110" s="29"/>
     </row>
-    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="29"/>
       <c r="B111" s="27"/>
       <c r="C111" s="38">
@@ -20256,7 +20238,7 @@
       <c r="J111" s="29"/>
       <c r="K111" s="29"/>
     </row>
-    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="29"/>
       <c r="B112" s="27"/>
       <c r="C112" s="35">
@@ -20277,7 +20259,7 @@
       <c r="J112" s="29"/>
       <c r="K112" s="29"/>
     </row>
-    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="29"/>
       <c r="B113" s="27"/>
       <c r="C113" s="38">
@@ -20298,7 +20280,7 @@
       <c r="J113" s="29"/>
       <c r="K113" s="29"/>
     </row>
-    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="29"/>
       <c r="B114" s="27"/>
       <c r="C114" s="35">
@@ -20319,7 +20301,7 @@
       <c r="J114" s="29"/>
       <c r="K114" s="29"/>
     </row>
-    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="29"/>
       <c r="B115" s="27"/>
       <c r="C115" s="38">
@@ -20340,7 +20322,7 @@
       <c r="J115" s="29"/>
       <c r="K115" s="29"/>
     </row>
-    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="29"/>
       <c r="B116" s="27"/>
       <c r="C116" s="35">
@@ -20361,7 +20343,7 @@
       <c r="J116" s="29"/>
       <c r="K116" s="29"/>
     </row>
-    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="29"/>
       <c r="B117" s="27"/>
       <c r="C117" s="38">
@@ -20382,7 +20364,7 @@
       <c r="J117" s="29"/>
       <c r="K117" s="29"/>
     </row>
-    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="29"/>
       <c r="B118" s="27"/>
       <c r="C118" s="35">
@@ -20403,7 +20385,7 @@
       <c r="J118" s="29"/>
       <c r="K118" s="29"/>
     </row>
-    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="29"/>
       <c r="B119" s="27"/>
       <c r="C119" s="38">
@@ -20424,7 +20406,7 @@
       <c r="J119" s="29"/>
       <c r="K119" s="29"/>
     </row>
-    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="29"/>
       <c r="B120" s="27"/>
       <c r="C120" s="35">
@@ -20445,7 +20427,7 @@
       <c r="J120" s="29"/>
       <c r="K120" s="29"/>
     </row>
-    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="29"/>
       <c r="B121" s="27"/>
       <c r="C121" s="38">
@@ -20466,7 +20448,7 @@
       <c r="J121" s="29"/>
       <c r="K121" s="29"/>
     </row>
-    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="29"/>
       <c r="B122" s="27"/>
       <c r="C122" s="35">
@@ -20487,7 +20469,7 @@
       <c r="J122" s="29"/>
       <c r="K122" s="29"/>
     </row>
-    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="29"/>
       <c r="B123" s="27"/>
       <c r="C123" s="38">
@@ -20508,7 +20490,7 @@
       <c r="J123" s="29"/>
       <c r="K123" s="29"/>
     </row>
-    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="29"/>
       <c r="B124" s="27"/>
       <c r="C124" s="35">
@@ -20529,7 +20511,7 @@
       <c r="J124" s="29"/>
       <c r="K124" s="29"/>
     </row>
-    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="29"/>
       <c r="B125" s="27"/>
       <c r="C125" s="38">
@@ -20550,7 +20532,7 @@
       <c r="J125" s="29"/>
       <c r="K125" s="29"/>
     </row>
-    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="29"/>
       <c r="B126" s="27"/>
       <c r="C126" s="35">
@@ -20571,7 +20553,7 @@
       <c r="J126" s="29"/>
       <c r="K126" s="29"/>
     </row>
-    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="29"/>
       <c r="B127" s="27"/>
       <c r="C127" s="38">
@@ -20592,7 +20574,7 @@
       <c r="J127" s="29"/>
       <c r="K127" s="29"/>
     </row>
-    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="29"/>
       <c r="B128" s="27"/>
       <c r="C128" s="35">
@@ -20613,7 +20595,7 @@
       <c r="J128" s="29"/>
       <c r="K128" s="29"/>
     </row>
-    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="29"/>
       <c r="B129" s="27"/>
       <c r="C129" s="38">
@@ -20634,7 +20616,7 @@
       <c r="J129" s="29"/>
       <c r="K129" s="29"/>
     </row>
-    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="29"/>
       <c r="B130" s="27"/>
       <c r="C130" s="35">
@@ -20655,7 +20637,7 @@
       <c r="J130" s="29"/>
       <c r="K130" s="29"/>
     </row>
-    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="29"/>
       <c r="B131" s="27"/>
       <c r="C131" s="38">
@@ -20676,7 +20658,7 @@
       <c r="J131" s="29"/>
       <c r="K131" s="29"/>
     </row>
-    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="7" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="29"/>
       <c r="B132" s="27"/>
       <c r="C132" s="35">
@@ -20697,7 +20679,7 @@
       <c r="J132" s="29"/>
       <c r="K132" s="29"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="38">
         <v>76</v>
       </c>
@@ -20711,7 +20693,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="35">
         <v>77</v>
       </c>
@@ -20725,7 +20707,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -20739,7 +20721,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="35">
         <v>79</v>
       </c>
